--- a/docs/xlsx/jobs-2026-09-11.xlsx
+++ b/docs/xlsx/jobs-2026-09-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="550">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,546 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Adventure Leader</t>
+  </si>
+  <si>
+    <t>City of Albuquerque | Parks and Recreation</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$12 per hour</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-adventure-leader-albuquerque-new-mexico/8974572086</t>
+  </si>
+  <si>
+    <t>Biological Science Technician</t>
+  </si>
+  <si>
+    <t>USDA APHIS Wildlife Services</t>
+  </si>
+  <si>
+    <t>Sioux Center, IA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$37,193 - $59,031 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biological-science-technician-sioux-center-iowa/9196330398</t>
+  </si>
+  <si>
+    <t>Clean Energy Program Analyst</t>
+  </si>
+  <si>
+    <t>Apex Analytics</t>
+  </si>
+  <si>
+    <t>Boulder, Remote</t>
+  </si>
+  <si>
+    <t>$75,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-clean-energy-program-analyst-boulder-remote/6491998735</t>
+  </si>
+  <si>
+    <t>Community Ag Coordinator</t>
+  </si>
+  <si>
+    <t>King Conservation District</t>
+  </si>
+  <si>
+    <t>Renton, WA</t>
+  </si>
+  <si>
+    <t>$75,155.67 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-ag-coordinator-renton-washington/9973408632</t>
+  </si>
+  <si>
+    <t>Ecological Restoration Crew Leader</t>
+  </si>
+  <si>
+    <t>Pizzo &amp; Associates LTD</t>
+  </si>
+  <si>
+    <t>St. Charles, IL</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecological-restoration-crew-leader-st-charles-illinois/4056276793</t>
+  </si>
+  <si>
+    <t>Emerging Leaders Council – Conservation Leadership Volunteer</t>
+  </si>
+  <si>
+    <t>Reef Expeditions</t>
+  </si>
+  <si>
+    <t>Cincinnati, OH</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-emerging-leaders-council--conservation-leadership-volunteer-cincinnati-ohio/5754607438</t>
+  </si>
+  <si>
+    <t>Enrollment Support Specialist (Administrative Assistant 2)</t>
+  </si>
+  <si>
+    <t>WA State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Lacey, WA</t>
+  </si>
+  <si>
+    <t>$44,856 - $59,760 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-enrollment-support-specialist-administrative-assistant-2-lacey-washington/6997189965</t>
+  </si>
+  <si>
+    <t>Environmental Communications &amp; Outreach Projects Manager</t>
+  </si>
+  <si>
+    <t>Morro Bay National Estuary Program</t>
+  </si>
+  <si>
+    <t>Morro Bay, CA</t>
+  </si>
+  <si>
+    <t>$30 - $33 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-communications--outreach-projects-manager-morro-bay-california/7706067292</t>
+  </si>
+  <si>
+    <t>Forester II / III (Silviculturist)</t>
+  </si>
+  <si>
+    <t>Kalispel Tribe of Indians</t>
+  </si>
+  <si>
+    <t>Usk, WA</t>
+  </si>
+  <si>
+    <t>$48,701 - $60,877 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forester-ii--iii-silviculturist-usk-washington/8651840867</t>
+  </si>
+  <si>
+    <t>Forestry Technician</t>
+  </si>
+  <si>
+    <t>Northern Stewards LLC</t>
+  </si>
+  <si>
+    <t>Waterbury, VT</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$18 - $22 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-technician-waterbury-vermont/6993809373</t>
+  </si>
+  <si>
+    <t>Geologist</t>
+  </si>
+  <si>
+    <t>North Wind Group</t>
+  </si>
+  <si>
+    <t>Los Alamos, NM</t>
+  </si>
+  <si>
+    <t>$78,000 - $118,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-geologist-los-alamos-new-mexico/6867710769</t>
+  </si>
+  <si>
+    <t>Geologist/Environmental Scientist</t>
+  </si>
+  <si>
+    <t>$70,000 - $88,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-geologistenvironmental-scientist-los-alamos-new-mexico/5244171235</t>
+  </si>
+  <si>
+    <t>Land Conservation Manager</t>
+  </si>
+  <si>
+    <t>The Land Trust for Santa Barbara County</t>
+  </si>
+  <si>
+    <t>Santa Barbara, CA</t>
+  </si>
+  <si>
+    <t>$110,000 - $130,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-conservation-manager-santa-barbara-california/6424587402</t>
+  </si>
+  <si>
+    <t>Lands Coordinator</t>
+  </si>
+  <si>
+    <t>Squam Lakes Conservation Society</t>
+  </si>
+  <si>
+    <t>Holderness, NH</t>
+  </si>
+  <si>
+    <t>$52,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lands-coordinator-holderness-new-hampshire/3214100227</t>
+  </si>
+  <si>
+    <t>Leadership Development Program (LDP)</t>
+  </si>
+  <si>
+    <t>The Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Las Vegas, NV</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$2,707.68 per month</t>
+  </si>
+  <si>
+    <t>forestry-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-leadership-development-program-ldp-las-vegas-nevada/3367084763</t>
+  </si>
+  <si>
+    <t>Marine and Land Based Heavy Equipment Operator</t>
+  </si>
+  <si>
+    <t>Kent Conservation District</t>
+  </si>
+  <si>
+    <t>Rehoboth Beach, DE</t>
+  </si>
+  <si>
+    <t>$39,874 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-and-land-based-heavy-equipment-operator-rehoboth-beach-delaware/7044271954</t>
+  </si>
+  <si>
+    <t>Marine Science Educator Aboard 80’ Schooner SoundWaters</t>
+  </si>
+  <si>
+    <t>SoundWaters, Inc.</t>
+  </si>
+  <si>
+    <t>Stamford, CT</t>
+  </si>
+  <si>
+    <t>$400 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-science-educator-aboard-80-schooner-soundwaters-stamford-connecticut/2681466036</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications Specialist</t>
+  </si>
+  <si>
+    <t>Save The Bay</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>$38.34 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marketing--communications-specialist-oakland-california/3989642826</t>
+  </si>
+  <si>
+    <t>Native Plant &amp; Plug Outside Sales Representative</t>
+  </si>
+  <si>
+    <t>Leland, IL</t>
+  </si>
+  <si>
+    <t>$80,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-native-plant--plug-outside-sales-representative-leland-illinois/5827689058</t>
+  </si>
+  <si>
+    <t>Naturalist Fellowship</t>
+  </si>
+  <si>
+    <t>Alaska Wildlife Conservation Center</t>
+  </si>
+  <si>
+    <t>Girdwood, AK</t>
+  </si>
+  <si>
+    <t>Volunteer position, housing provided</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-naturalist-fellowship-girdwood-alaska/3167547692</t>
+  </si>
+  <si>
+    <t>Oceans Campaigner</t>
+  </si>
+  <si>
+    <t>Center for Biological Diversity</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>$55,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-oceans-campaigner-remote-remote/5080003025</t>
+  </si>
+  <si>
+    <t>Open Space Technician</t>
+  </si>
+  <si>
+    <t>Midpeninsula Regional Open Space District</t>
+  </si>
+  <si>
+    <t>Cupertino, CA</t>
+  </si>
+  <si>
+    <t>$94,689 - $118,268 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-open-space-technician-cupertino-ca-california/8984941213</t>
+  </si>
+  <si>
+    <t>Operations &amp; Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Western Resilience Center</t>
+  </si>
+  <si>
+    <t>Steamboat Springs, CO</t>
+  </si>
+  <si>
+    <t>$58,000 - $68,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations--engagement-coordinator-steamboat-springs-colorado/1527705667</t>
+  </si>
+  <si>
+    <t>Paid AmeriCorps Volunteer</t>
+  </si>
+  <si>
+    <t>AmeriCorps READY</t>
+  </si>
+  <si>
+    <t>Detroit, MI</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-paid-americorps-volunteer-detroit-michigan/2531620978</t>
+  </si>
+  <si>
+    <t>Project-Based Grant Writer</t>
+  </si>
+  <si>
+    <t>Boulder Mushroom</t>
+  </si>
+  <si>
+    <t>Boulder, CO</t>
+  </si>
+  <si>
+    <t>$25 - $35 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-project-based-grant-writer-boulder-colorado/7509314392</t>
+  </si>
+  <si>
+    <t>Resource Technician</t>
+  </si>
+  <si>
+    <t>Deep Portage Learning Center</t>
+  </si>
+  <si>
+    <t>Hackensack, MN</t>
+  </si>
+  <si>
+    <t>$14 - $17 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resource-technician-hackensack-minnesota/7094275734</t>
+  </si>
+  <si>
+    <t>Summer 2027 Legal Clerk</t>
+  </si>
+  <si>
+    <t>The Wilderness Society</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-summer-2027-legal-clerk-remote-remote/2262880853</t>
+  </si>
+  <si>
+    <t>Account Manager, Fire Fighter Partnerships</t>
+  </si>
+  <si>
+    <t>Muscular Dystrophy Association</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d369e01137244348d47ee8f1bd97739-account-manager-fire-fighter-partnerships-muscular-dystrophy-association-chicago</t>
+  </si>
+  <si>
+    <t>Associate Director, Campaign Strategy</t>
+  </si>
+  <si>
+    <t>Playwrights Horizons</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/067070560e284c7e9a150947bf09baf2-associate-director-campaign-strategy-playwrights-horizons-new-york</t>
+  </si>
+  <si>
+    <t>Associate Director, The Housing Lab</t>
+  </si>
+  <si>
+    <t>Impact Justice</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Prison Reform, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49234d48438f4551bca02fc0125ccf8c-associate-director-the-housing-lab-impact-justice-oakland</t>
+  </si>
+  <si>
+    <t>Communications &amp; Content Associate (leave replacement)</t>
+  </si>
+  <si>
+    <t>Pinewood School</t>
+  </si>
+  <si>
+    <t>Los Altos, California</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/566ad5224c214e5d82db65f696e33ec2-communications-content-associate-leave-replacement-pinewood-school-los-altos</t>
+  </si>
+  <si>
     <t>Communications Manager</t>
   </si>
   <si>
@@ -49,36 +589,756 @@
     <t>Toamasina, Atsinanana, MG</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Education, Science Technology</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/9ce21f6d2e7b4630886c5536871dd904-communications-manager-onja-toamasina</t>
   </si>
   <si>
+    <t>Association for Neighborhood and Housing Development</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea1ccfc4650747079e96dd353f2a6f2d-communications-manager-association-for-neighborhood-and-housing-development-new-york</t>
+  </si>
+  <si>
+    <t>Communications Specialist</t>
+  </si>
+  <si>
+    <t>New American Leaders</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/22d5fba17b9442998512234754dc48de-communications-specialist-new-american-leaders-new-york</t>
+  </si>
+  <si>
+    <t>Community Health Nurse</t>
+  </si>
+  <si>
+    <t>Neighborhood House</t>
+  </si>
+  <si>
+    <t>Tukwila, Washington</t>
+  </si>
+  <si>
+    <t>USD 43.97 - 48.83/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2d1123f13e7430dbb7888dcd910502a-community-health-nurse-neighborhood-house-tukwila</t>
+  </si>
+  <si>
+    <t>Content Specialist (Castle Hill YMCA)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ea4e6f76d58473f874e0d29b52cf5f6-content-specialist-castle-hill-ymca-ymca-of-greater-new-york-bronx-county</t>
+  </si>
+  <si>
+    <t>Deputy Director of Individual Giving</t>
+  </si>
+  <si>
+    <t>Center on Budget and Policy Priorities</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57827806db35418487030293543fd26c-deputy-director-of-individual-giving-center-on-budget-and-policy-priorities-washington</t>
+  </si>
+  <si>
+    <t>Deputy Director, Support Transition</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union</t>
+  </si>
+  <si>
+    <t>USD 196369.00 - 196369.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c2af32359fd44339def907df6415782-deputy-director-support-transition-american-civil-liberties-union-new-york</t>
+  </si>
+  <si>
+    <t>Development Assistant</t>
+  </si>
+  <si>
+    <t>Outright International</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/330ff7fcea944b828cd996717149745f-development-assistant-outright-international-new-york</t>
+  </si>
+  <si>
+    <t>Development Coordinator - Los Angeles-based Cat Rescue</t>
+  </si>
+  <si>
+    <t>Stray Cat Alliance</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/334087dc5b144fc6b27cef820c1918c1-development-coordinator-los-angeles-based-cat-rescue-stray-cat-alliance-los-angeles</t>
+  </si>
+  <si>
+    <t>Development Coordinator, Part-Time Temporary</t>
+  </si>
+  <si>
+    <t>Breakthrough T1D (formerly known as JDRF)</t>
+  </si>
+  <si>
+    <t>Remote (Wilmington, North Carolina)</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Philanthropy, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e42d81b4649c40cea4183501ee62ea8e-development-coordinator-part-time-temporary-breakthrough-t1d-formerly-known-as-jdrf-wilmington</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Innocence &amp; Justice Louisiana</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d93db5c818540519d9cade565b9d964-development-director-innocence-justice-louisiana-new-orleans</t>
+  </si>
+  <si>
+    <t>Director - Film, Culture &amp; Community</t>
+  </si>
+  <si>
+    <t>Japan Society</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b5252cf6a78432f88d96ce629e3fbd0-director-film-culture-community-japan-society-new-york</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Anthos Home</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be068751cb3549298c0576986250531a-director-of-communications-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>One To World</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/51bafbb504f44deebe7f3c7966a5d726-director-of-development-one-to-world-new-york</t>
+  </si>
+  <si>
+    <t>Director of Digital Communications</t>
+  </si>
+  <si>
+    <t>Guttmacher Institute</t>
+  </si>
+  <si>
+    <t>USD 188800.00 - 217100.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e9fd3db084d4262a0928f51e5992172-director-of-digital-communications-guttmacher-institute-new-york</t>
+  </si>
+  <si>
+    <t>Director of Finance &amp; Operations</t>
+  </si>
+  <si>
+    <t>Southern Service Workers Education Fund, Inc.</t>
+  </si>
+  <si>
+    <t>Remote (North Carolina)</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d1cd82e7dd9c43b7aa3f902e554faba5-director-of-finance-operations-southern-service-workers-education-fund-inc-durham</t>
+  </si>
+  <si>
+    <t>Director of Global Advocacy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a21ecce4e3084086aa93c7641adb9311-director-of-global-advocacy-guttmacher-institute-new-york</t>
+  </si>
+  <si>
+    <t>Director of Government Relations</t>
+  </si>
+  <si>
+    <t>Public Lands Alliance</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37f847d5ce0d4537b66e75f136389204-director-of-government-relations-public-lands-alliance-washington</t>
+  </si>
+  <si>
+    <t>Director of Human Resources</t>
+  </si>
+  <si>
+    <t>The Children's Home Society of New Jersey</t>
+  </si>
+  <si>
+    <t>Trenton, New Jersey</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74a79764d0704a94846b8397413a35ae-director-of-human-resources-the-childrens-home-society-of-new-jersey-trenton</t>
+  </si>
+  <si>
+    <t>Director of Technology and Data</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b270cea6901f45fb85c0112559dc43b2-director-of-technology-and-data-the-childrens-home-society-of-new-jersey-trenton</t>
+  </si>
+  <si>
+    <t>Director of the Institute for LGBTQIA+ Community Engagement and Public Hist</t>
+  </si>
+  <si>
+    <t>LaGuardia Community College</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 91878.00 - 95506.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f19780aa4fbf4147a3f340dabd49bcc7-director-of-the-institute-for-lgbtqia-community-engagement-and-public-hist-laguardia-community-college-queens-county</t>
+  </si>
+  <si>
+    <t>Director or Senior Director of Government Relations, New York State</t>
+  </si>
+  <si>
+    <t>Open Space Institute</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd8a4bbcbaca4ac4ac8d31ea70865f68-director-or-senior-director-of-government-relations-new-york-state-open-space-institute-albany</t>
+  </si>
+  <si>
+    <t>Director, Communications, Climate &amp; Energy Program</t>
+  </si>
+  <si>
+    <t>Third Way</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85d38a308f444c90add162e318e186f0-director-communications-climate-energy-program-third-way-washington</t>
+  </si>
+  <si>
+    <t>English for New Bostonians: Director of Institutional Giving</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/9d54a5166c5648dbb06cc3b2cfa631b4-english-for-new-bostonians-director-of-institutional-giving-boston</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>New England Joint Board UNITE HERE</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2cb41387f065444e96f69b2f5d907b13-executive-assistant-new-england-joint-board-unite-here-boston</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Capital Development Services</t>
+  </si>
+  <si>
+    <t>Winston-Salem, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/074cd7c2fc654e39bc73a133f411977f-executive-director-capital-development-services-winston-salem</t>
+  </si>
+  <si>
+    <t>Florida Rights Restoration Coalition</t>
+  </si>
+  <si>
+    <t>Orlando, Florida</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1038f006d8a140f298a368d0f652c6e9-executive-director-florida-rights-restoration-coalition-orlando</t>
+  </si>
+  <si>
+    <t>Facilitador/a Niño y Niña - Filial Mendoza</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Mendoza, Mendoza, AR</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/920cb0bda124460f9912b0815742d0e3-facilitadora-nino-y-nina-filial-mendoza-aldeas-infantiles-sos-argentina-mendoza</t>
+  </si>
+  <si>
+    <t>Family Intervention Specialist</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Bend, Oregon</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92ce3b22e9e24d47a58ad4070587c953-family-intervention-specialist-youth-villages-bend</t>
+  </si>
+  <si>
+    <t>Family Intervention Specialist - Baldwin County, AL</t>
+  </si>
+  <si>
+    <t>Daphne, Alabama</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca06fa4d639e4a06963e3aaea1ad30f4-family-intervention-specialist-baldwin-county-al-youth-villages-daphne</t>
+  </si>
+  <si>
+    <t>Family Intervention Specialist - Oregon Coast</t>
+  </si>
+  <si>
+    <t>Tillamook, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54877d3262d54a3db15428c6d38a21a6-family-intervention-specialist-oregon-coast-youth-villages-tillamook</t>
+  </si>
+  <si>
+    <t>FINANCE AND ACCOUNTING MANAGER</t>
+  </si>
+  <si>
+    <t>Envision Consulting</t>
+  </si>
+  <si>
+    <t>USD 80314.00 - 124487.00/year</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2f485d55ca134b9b9cee7120e47f4a8b-finance-and-accounting-manager-envision-consulting-washington</t>
+  </si>
+  <si>
+    <t>Financial Manager</t>
+  </si>
+  <si>
+    <t>Northwest Center for Alternatives to Pesticides</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>USD 35971.00 - 35971.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb1e0dcdd7784d2c8e5389ba9af30081-financial-manager-northwest-center-for-alternatives-to-pesticides-eugene</t>
+  </si>
+  <si>
+    <t>Global Fundraising Director</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3632210ea584097979f8bf31d5340a7-global-fundraising-director-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Grants &amp; Contracts Associate</t>
+  </si>
+  <si>
+    <t>Great Plains Institute</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5432278d2884e66a798118314c6bb45-grants-contracts-associate-great-plains-institute-minneapolis</t>
+  </si>
+  <si>
+    <t>Head of Revenue Operations</t>
+  </si>
+  <si>
+    <t>FIND</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b874260b6494883a76e3d50dad402b9-head-of-revenue-operations-find-calabar</t>
+  </si>
+  <si>
     <t>Hiring Manager</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/eecaa3e9c1344592b569f7f6a1c0b71f-hiring-manager-onja-toamasina</t>
   </si>
   <si>
+    <t>Human Resource Manager</t>
+  </si>
+  <si>
+    <t>American Association of State Highway &amp; Transportation Officials</t>
+  </si>
+  <si>
+    <t>USD 102000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ce57783442e4f3aa49e2d4dcf825675-human-resource-manager-american-association-of-state-highway-transportation-officials-washington</t>
+  </si>
+  <si>
+    <t>Legal Content Director</t>
+  </si>
+  <si>
+    <t>Illinois Legal Aid Online (ILAO)</t>
+  </si>
+  <si>
+    <t>Remote (Illinois)</t>
+  </si>
+  <si>
+    <t>USD 94000.00 - 104000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee3caafb2f79496eb5ae5832311a28cb-legal-content-director-illinois-legal-aid-online-ilao-chicago</t>
+  </si>
+  <si>
     <t>Legal Counsel - International</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/3ed494ba0e2f4d67915732477be6ce6f-legal-counsel-international-onja-toamasina</t>
   </si>
   <si>
+    <t>Legal Justice Advocate</t>
+  </si>
+  <si>
+    <t>Women's Community Center</t>
+  </si>
+  <si>
+    <t>Brattleboro, Vermont</t>
+  </si>
+  <si>
+    <t>USD 22.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7077ce228b354c70aef07e96205c4ec1-legal-justice-advocate-womens-community-center-brattleboro</t>
+  </si>
+  <si>
+    <t>Local Food Access Warehouse Packer</t>
+  </si>
+  <si>
+    <t>The People's Market</t>
+  </si>
+  <si>
+    <t>Hyattsville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/686301d166e64e6e9cf99ee3b43ef39d-local-food-access-warehouse-packer-the-peoples-market-hyattsville</t>
+  </si>
+  <si>
+    <t>Logistics &amp; Resources Manager</t>
+  </si>
+  <si>
+    <t>Beth-El Farm Worker Ministry, Inc.</t>
+  </si>
+  <si>
+    <t>Wimauma, Florida</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Immigrants Or Refugees, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7fd4feb53f6b468cbd9b07d7e6bcfb7e-logistics-resources-manager-beth-el-farm-worker-ministry-inc-wimauma</t>
+  </si>
+  <si>
+    <t>Manager, Programs and Grants</t>
+  </si>
+  <si>
+    <t>Northeast Business Group on Health</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58e648c8ba584c40a9f537d0f3b0e599-manager-programs-and-grants-northeast-business-group-on-health-new-york</t>
+  </si>
+  <si>
+    <t>Marketing and Communications Coordinator</t>
+  </si>
+  <si>
+    <t>The Lotus Institute</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b8d6be561d9478285d460617e5a6cbe-marketing-and-communications-coordinator-the-lotus-institute-pataskala</t>
+  </si>
+  <si>
+    <t>Mobile Market Operator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/5b74ca024e3f41fc8c01fbfa6d3661a7-mobile-market-operator-the-peoples-market-hyattsville</t>
+  </si>
+  <si>
+    <t>National Director, Mental Health Equity &amp; Engagement</t>
+  </si>
+  <si>
+    <t>NAMI (National Alliance on Mental Illness)</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2272d0a312644e28ab2b322f46adb92-national-director-mental-health-equity-engagement-nami-national-alliance-on-mental-illness-arlington</t>
+  </si>
+  <si>
+    <t>Nonprofit Operations Specialist</t>
+  </si>
+  <si>
+    <t>The Funding Studio</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Entrepreneurship, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8d8d146165943cb9227b3bb22d797cb-nonprofit-operations-specialist-the-funding-studio-phoenix</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Advancing Real Change, Inc.</t>
+  </si>
+  <si>
+    <t>Jacksonville, Florida</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b34c875c1304eae82a052f46bb59873-operations-manager-advancing-real-change-inc-jacksonville</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47b6d934fe0648c99b89e24ede1e0554-operations-manager-advancing-real-change-inc-baltimore</t>
+  </si>
+  <si>
+    <t>Birmingham, Alabama</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1650e6b1afd545b1b8d99d727987cab7-operations-manager-advancing-real-change-inc-birmingham</t>
+  </si>
+  <si>
+    <t>Operations Manager (Part time, contract)</t>
+  </si>
+  <si>
+    <t>AWE Global (formerly Artistri Sud)</t>
+  </si>
+  <si>
+    <t>CAD 25000.00 - 25000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b32b658ed7c45c1a1c9912e5fcc0317-operations-manager-part-time-contract-awe-global-formerly-artistri-sud-montreal</t>
+  </si>
+  <si>
     <t>Ostrich Bay Mobile Outreach Coordinator</t>
   </si>
   <si>
@@ -88,9 +1348,6 @@
     <t>Bremerton, Washington</t>
   </si>
   <si>
-    <t>USD 30.00 - 30.00/hour</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/8ff4c02330fe453bb5d3dc04315649fe-ostrich-bay-mobile-outreach-coordinator-the-peoples-harm-reduction-alliance-phra-bremerton</t>
   </si>
   <si>
@@ -109,6 +1366,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/6f42d28c976047e6b961baefb6b06ab6-overdose-prevention-specialist-the-peoples-harm-reduction-alliance-phra-seattle</t>
   </si>
   <si>
+    <t>Philanthropic Advisor</t>
+  </si>
+  <si>
+    <t>Baylor University</t>
+  </si>
+  <si>
+    <t>Waco, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b327c229ff32481992ab855b67432780-philanthropic-advisor-baylor-university-waco</t>
+  </si>
+  <si>
+    <t>PRN Residential Master's Level Counselor</t>
+  </si>
+  <si>
+    <t>Douglasville, Georgia</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9ef8f4c992c410e9deb867cbbc69eb8-prn-residential-masters-level-counselor-youth-villages-douglasville</t>
+  </si>
+  <si>
+    <t>PROGRAM ASSISTANT</t>
+  </si>
+  <si>
+    <t>Youth Justice Network</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/195c8dda8a504322afed2dbe6c643cc2-program-assistant-youth-justice-network-new-york</t>
+  </si>
+  <si>
     <t>Program Coordinator</t>
   </si>
   <si>
@@ -122,6 +1415,255 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/dc67906db4254c7685bc256b10af98dc-program-coordinator-everyone-on-los-angeles</t>
+  </si>
+  <si>
+    <t>Program Director, The Menopause Project</t>
+  </si>
+  <si>
+    <t>Crime Safety, Prison Reform, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7fce4536852f41a488df6601bd52fd7c-program-director-the-menopause-project-impact-justice-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77404bc1c98b4ea28f25e26596447758-program-director-the-menopause-project-impact-justice-oakland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d7195500b8242b1a83639709c48bdf9-program-director-the-menopause-project-impact-justice-washington</t>
+  </si>
+  <si>
+    <t>Red Hook on the Road Program Manager</t>
+  </si>
+  <si>
+    <t>Brooklyn Workforce Innovations</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 72500.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43f8a19cb462475784c96f1b9d2d5222-red-hook-on-the-road-program-manager-brooklyn-workforce-innovations-kings-county</t>
+  </si>
+  <si>
+    <t>Registered Nurse</t>
+  </si>
+  <si>
+    <t>USD 37.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6489ba462c04d5a8d45e41fb575d6e4-registered-nurse-youth-villages-douglasville</t>
+  </si>
+  <si>
+    <t>Research Analyst - New Organizing SEIU Healthcare Michigan (HCMI)</t>
+  </si>
+  <si>
+    <t>SEIU</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/045e9b884091495abb49ba012a8651f0-research-analyst-new-organizing-seiu-healthcare-michigan-hcmi-seiu-detroit</t>
+  </si>
+  <si>
+    <t>Seasonal Food Team Member</t>
+  </si>
+  <si>
+    <t>Bread for the City</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 24.04 - 24.04/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80c99c4f20a6493f82aaeaf7881ad045-seasonal-food-team-member-bread-for-the-city-washington</t>
+  </si>
+  <si>
+    <t>Senior Business Development Manager</t>
+  </si>
+  <si>
+    <t>Women First Digital</t>
+  </si>
+  <si>
+    <t>Remote (BE)</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/cdc1c741c83746318e441b73d3d63f98-senior-business-development-manager-women-first-digital-brussels</t>
+  </si>
+  <si>
+    <t>Remote (GH)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/c2658419fec543ec931ff298fd66ede7-senior-business-development-manager-women-first-digital-accra</t>
+  </si>
+  <si>
+    <t>Remote (SN)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/c085ffc1973343edb9c5978b15a9780f-senior-business-development-manager-women-first-digital-dakar</t>
+  </si>
+  <si>
+    <t>Remote (BR)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/bd5cc1e959be4785bd869f3a3a5c0f56-senior-business-development-manager-women-first-digital-sao-paulo</t>
+  </si>
+  <si>
+    <t>Remote (GB)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/6c2f50b787614309b28c9da19a425f3d-senior-business-development-manager-women-first-digital-london</t>
+  </si>
+  <si>
+    <t>Remote (MX)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/35f00139625a4612ade950950f8ce21a-senior-business-development-manager-women-first-digital-mexico-city</t>
+  </si>
+  <si>
+    <t>Remote (NG)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/29da4338a9b3480ba8120569b2eaec9c-senior-business-development-manager-women-first-digital-lagos</t>
+  </si>
+  <si>
+    <t>Senior Program Manager - Global Rights and Grantmaking</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Lgbtq, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd95c0cfe2264140966c1a8bf561731d-senior-program-manager-global-rights-and-grantmaking-outright-international-new-york</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney, Family Defense Practice, Bronx</t>
+  </si>
+  <si>
+    <t>Center for Family Representation, Inc.</t>
+  </si>
+  <si>
+    <t>USD 110600.00 - 132400.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57c05df3fee24d9f8ddd476925598c31-senior-staff-attorney-family-defense-practice-bronx-center-for-family-representation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Special Education Teacher - **Immediate Hire**</t>
+  </si>
+  <si>
+    <t>YouthBuild Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5fc5fd907c24662aff9c4896e0bff5b-special-education-teacher-immediate-hire-youthbuild-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Technical Advisor – International Business &amp; Economic Development</t>
+  </si>
+  <si>
+    <t>USD 97038.00 - 126024.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02b7722252ea47f586326879245be204-technical-advisor-international-business-economic-development-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Vice President of Finance and Administration</t>
+  </si>
+  <si>
+    <t>National Center for LGBTQ Rights</t>
+  </si>
+  <si>
+    <t>USD 164690.00 - 177872.00/year</t>
+  </si>
+  <si>
+    <t>Lgbtq, Immigrants Or Refugees, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16d75dd85f734771a9f38f3b1e8d92e2-vice-president-of-finance-and-administration-national-center-for-lgbtq-rights-san-francisco</t>
+  </si>
+  <si>
+    <t>Vice President, Business Development</t>
+  </si>
+  <si>
+    <t>BME Strategies</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5df6a44fb9ef4e008919c759705998bf-vice-president-business-development-bme-strategies-north-andover</t>
+  </si>
+  <si>
+    <t>Vice President, Membership</t>
+  </si>
+  <si>
+    <t>American Pharmacists Association</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 167000.00 - 207919.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eec2370fbcdc476db7931bca870e8992-vice-president-membership-american-pharmacists-association-washington</t>
+  </si>
+  <si>
+    <t>Workforce Planning and Org Design Consultant</t>
+  </si>
+  <si>
+    <t>World Food Programme</t>
+  </si>
+  <si>
+    <t>Panama City, Panamá Province, PA</t>
+  </si>
+  <si>
+    <t>Poverty, Disaster Relief, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c65ef60a3cb443e288230b4f814c1215-workforce-planning-and-org-design-consultant-world-food-programme-panama-city</t>
+  </si>
+  <si>
+    <t>Writing Instructor</t>
+  </si>
+  <si>
+    <t>Minds Matter Boston</t>
+  </si>
+  <si>
+    <t>USD 100.00/week</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a373435632334efba3f2446b4daf8d35-writing-instructor-minds-matter-boston-boston</t>
   </si>
 </sst>
 </file>
@@ -507,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -546,8 +2088,658 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>143</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" t="s">
+        <v>160</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -603,7 +2795,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -644,140 +2836,1957 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>167</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>186</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>191</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>195</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>35</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" t="s">
+        <v>219</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F13" t="s">
+        <v>229</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F14" t="s">
+        <v>235</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" t="s">
+        <v>245</v>
+      </c>
+      <c r="D16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" t="s">
+        <v>246</v>
+      </c>
+      <c r="F16" t="s">
+        <v>247</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B17" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" t="s">
+        <v>256</v>
+      </c>
+      <c r="F18" t="s">
+        <v>257</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" t="s">
+        <v>261</v>
+      </c>
+      <c r="F19" t="s">
+        <v>262</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" t="s">
+        <v>266</v>
+      </c>
+      <c r="F20" t="s">
+        <v>267</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B21" t="s">
+        <v>270</v>
+      </c>
+      <c r="C21" t="s">
+        <v>271</v>
+      </c>
+      <c r="D21" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" t="s">
+        <v>272</v>
+      </c>
+      <c r="F21" t="s">
+        <v>273</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>275</v>
+      </c>
+      <c r="B22" t="s">
+        <v>265</v>
+      </c>
+      <c r="C22" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" t="s">
+        <v>266</v>
+      </c>
+      <c r="F22" t="s">
+        <v>267</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B23" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" t="s">
+        <v>279</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>281</v>
+      </c>
+      <c r="B24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F24" t="s">
+        <v>284</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>286</v>
+      </c>
+      <c r="B25" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" t="s">
+        <v>283</v>
+      </c>
+      <c r="D25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" t="s">
+        <v>287</v>
+      </c>
+      <c r="F25" t="s">
+        <v>284</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>289</v>
+      </c>
+      <c r="B26" t="s">
+        <v>290</v>
+      </c>
+      <c r="C26" t="s">
+        <v>291</v>
+      </c>
+      <c r="D26" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" t="s">
+        <v>292</v>
+      </c>
+      <c r="F26" t="s">
+        <v>293</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>295</v>
+      </c>
+      <c r="B27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C27" t="s">
+        <v>297</v>
+      </c>
+      <c r="D27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27" t="s">
+        <v>298</v>
+      </c>
+      <c r="F27" t="s">
+        <v>299</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>301</v>
+      </c>
+      <c r="B28" t="s">
+        <v>302</v>
+      </c>
+      <c r="C28" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F28" t="s">
+        <v>304</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>307</v>
+      </c>
+      <c r="D29" t="s">
+        <v>165</v>
+      </c>
+      <c r="E29" t="s">
+        <v>308</v>
+      </c>
+      <c r="F29" t="s">
+        <v>309</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>311</v>
+      </c>
+      <c r="B30" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" t="s">
+        <v>313</v>
+      </c>
+      <c r="D30" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" t="s">
+        <v>314</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>316</v>
+      </c>
+      <c r="B31" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" t="s">
+        <v>318</v>
+      </c>
+      <c r="D31" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" t="s">
+        <v>319</v>
+      </c>
+      <c r="F31" t="s">
+        <v>320</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>316</v>
+      </c>
+      <c r="B32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C32" t="s">
+        <v>323</v>
+      </c>
+      <c r="D32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" t="s">
+        <v>324</v>
+      </c>
+      <c r="F32" t="s">
+        <v>325</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>327</v>
+      </c>
+      <c r="B33" t="s">
+        <v>328</v>
+      </c>
+      <c r="C33" t="s">
+        <v>329</v>
+      </c>
+      <c r="D33" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" t="s">
+        <v>330</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>332</v>
+      </c>
+      <c r="B34" t="s">
+        <v>333</v>
+      </c>
+      <c r="C34" t="s">
+        <v>334</v>
+      </c>
+      <c r="D34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" t="s">
+        <v>335</v>
+      </c>
+      <c r="F34" t="s">
+        <v>336</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>338</v>
+      </c>
+      <c r="B35" t="s">
+        <v>333</v>
+      </c>
+      <c r="C35" t="s">
+        <v>339</v>
+      </c>
+      <c r="D35" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" t="s">
+        <v>340</v>
+      </c>
+      <c r="F35" t="s">
+        <v>336</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>342</v>
+      </c>
+      <c r="B36" t="s">
+        <v>333</v>
+      </c>
+      <c r="C36" t="s">
+        <v>343</v>
+      </c>
+      <c r="D36" t="s">
+        <v>165</v>
+      </c>
+      <c r="E36" t="s">
+        <v>335</v>
+      </c>
+      <c r="F36" t="s">
+        <v>336</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>345</v>
+      </c>
+      <c r="B37" t="s">
+        <v>346</v>
+      </c>
+      <c r="C37" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" t="s">
+        <v>165</v>
+      </c>
+      <c r="E37" t="s">
+        <v>347</v>
+      </c>
+      <c r="F37" t="s">
+        <v>348</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>350</v>
+      </c>
+      <c r="B38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C38" t="s">
+        <v>352</v>
+      </c>
+      <c r="D38" t="s">
+        <v>212</v>
+      </c>
+      <c r="E38" t="s">
+        <v>353</v>
+      </c>
+      <c r="F38" t="s">
+        <v>299</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>355</v>
+      </c>
+      <c r="B39" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" t="s">
+        <v>357</v>
+      </c>
+      <c r="D39" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" t="s">
+        <v>358</v>
+      </c>
+      <c r="F39" t="s">
+        <v>359</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>361</v>
+      </c>
+      <c r="B40" t="s">
+        <v>362</v>
+      </c>
+      <c r="C40" t="s">
+        <v>363</v>
+      </c>
+      <c r="D40" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" t="s">
+        <v>364</v>
+      </c>
+      <c r="F40" t="s">
+        <v>299</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>366</v>
+      </c>
+      <c r="B41" t="s">
+        <v>367</v>
+      </c>
+      <c r="C41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" t="s">
+        <v>314</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>369</v>
+      </c>
+      <c r="B42" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" t="s">
+        <v>165</v>
+      </c>
+      <c r="E42" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" t="s">
+        <v>44</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>371</v>
+      </c>
+      <c r="B43" t="s">
+        <v>372</v>
+      </c>
+      <c r="C43" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" t="s">
+        <v>165</v>
+      </c>
+      <c r="E43" t="s">
+        <v>373</v>
+      </c>
+      <c r="F43" t="s">
+        <v>374</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>376</v>
+      </c>
+      <c r="B44" t="s">
+        <v>377</v>
+      </c>
+      <c r="C44" t="s">
+        <v>378</v>
+      </c>
+      <c r="D44" t="s">
+        <v>165</v>
+      </c>
+      <c r="E44" t="s">
+        <v>379</v>
+      </c>
+      <c r="F44" t="s">
+        <v>380</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>382</v>
+      </c>
+      <c r="B45" t="s">
+        <v>189</v>
+      </c>
+      <c r="C45" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" t="s">
+        <v>212</v>
+      </c>
+      <c r="E45" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" t="s">
+        <v>44</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>384</v>
+      </c>
+      <c r="B46" t="s">
+        <v>385</v>
+      </c>
+      <c r="C46" t="s">
+        <v>386</v>
+      </c>
+      <c r="D46" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" t="s">
+        <v>387</v>
+      </c>
+      <c r="F46" t="s">
+        <v>388</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>390</v>
+      </c>
+      <c r="B47" t="s">
+        <v>391</v>
+      </c>
+      <c r="C47" t="s">
+        <v>392</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" t="s">
+        <v>393</v>
+      </c>
+      <c r="F47" t="s">
+        <v>394</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>396</v>
+      </c>
+      <c r="B48" t="s">
+        <v>397</v>
+      </c>
+      <c r="C48" t="s">
+        <v>398</v>
+      </c>
+      <c r="D48" t="s">
+        <v>165</v>
+      </c>
+      <c r="E48" t="s">
+        <v>399</v>
+      </c>
+      <c r="F48" t="s">
+        <v>400</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>402</v>
+      </c>
+      <c r="B49" t="s">
+        <v>403</v>
+      </c>
+      <c r="C49" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" t="s">
+        <v>165</v>
+      </c>
+      <c r="E49" t="s">
+        <v>404</v>
+      </c>
+      <c r="F49" t="s">
+        <v>405</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>407</v>
+      </c>
+      <c r="B50" t="s">
+        <v>408</v>
+      </c>
+      <c r="C50" t="s">
+        <v>164</v>
+      </c>
+      <c r="D50" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" t="s">
+        <v>409</v>
+      </c>
+      <c r="F50" t="s">
+        <v>410</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>412</v>
+      </c>
+      <c r="B51" t="s">
+        <v>391</v>
+      </c>
+      <c r="C51" t="s">
+        <v>392</v>
+      </c>
+      <c r="D51" t="s">
+        <v>212</v>
+      </c>
+      <c r="E51" t="s">
+        <v>393</v>
+      </c>
+      <c r="F51" t="s">
+        <v>394</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>414</v>
+      </c>
+      <c r="B52" t="s">
+        <v>415</v>
+      </c>
+      <c r="C52" t="s">
+        <v>416</v>
+      </c>
+      <c r="D52" t="s">
+        <v>165</v>
+      </c>
+      <c r="E52" t="s">
+        <v>417</v>
+      </c>
+      <c r="F52" t="s">
+        <v>418</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>420</v>
+      </c>
+      <c r="B53" t="s">
+        <v>421</v>
+      </c>
+      <c r="C53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" t="s">
+        <v>422</v>
+      </c>
+      <c r="E53" t="s">
+        <v>423</v>
+      </c>
+      <c r="F53" t="s">
+        <v>424</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>426</v>
+      </c>
+      <c r="B54" t="s">
+        <v>427</v>
+      </c>
+      <c r="C54" t="s">
+        <v>428</v>
+      </c>
+      <c r="D54" t="s">
+        <v>165</v>
+      </c>
+      <c r="E54" t="s">
+        <v>429</v>
+      </c>
+      <c r="F54" t="s">
+        <v>430</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>426</v>
+      </c>
+      <c r="B55" t="s">
+        <v>427</v>
+      </c>
+      <c r="C55" t="s">
+        <v>432</v>
+      </c>
+      <c r="D55" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" t="s">
+        <v>429</v>
+      </c>
+      <c r="F55" t="s">
+        <v>430</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>426</v>
+      </c>
+      <c r="B56" t="s">
+        <v>427</v>
+      </c>
+      <c r="C56" t="s">
+        <v>434</v>
+      </c>
+      <c r="D56" t="s">
+        <v>165</v>
+      </c>
+      <c r="E56" t="s">
+        <v>429</v>
+      </c>
+      <c r="F56" t="s">
+        <v>430</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>436</v>
+      </c>
+      <c r="B57" t="s">
+        <v>437</v>
+      </c>
+      <c r="C57" t="s">
+        <v>164</v>
+      </c>
+      <c r="D57" t="s">
+        <v>422</v>
+      </c>
+      <c r="E57" t="s">
+        <v>438</v>
+      </c>
+      <c r="F57" t="s">
+        <v>439</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>441</v>
+      </c>
+      <c r="B58" t="s">
+        <v>442</v>
+      </c>
+      <c r="C58" t="s">
+        <v>443</v>
+      </c>
+      <c r="D58" t="s">
+        <v>165</v>
+      </c>
+      <c r="E58" t="s">
+        <v>423</v>
+      </c>
+      <c r="F58" t="s">
+        <v>44</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>445</v>
+      </c>
+      <c r="B59" t="s">
+        <v>442</v>
+      </c>
+      <c r="C59" t="s">
+        <v>446</v>
+      </c>
+      <c r="D59" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" t="s">
+        <v>447</v>
+      </c>
+      <c r="F59" t="s">
+        <v>448</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>450</v>
+      </c>
+      <c r="B60" t="s">
+        <v>451</v>
+      </c>
+      <c r="C60" t="s">
+        <v>452</v>
+      </c>
+      <c r="D60" t="s">
+        <v>165</v>
+      </c>
+      <c r="E60" t="s">
+        <v>44</v>
+      </c>
+      <c r="F60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>454</v>
+      </c>
+      <c r="B61" t="s">
+        <v>333</v>
+      </c>
+      <c r="C61" t="s">
+        <v>455</v>
+      </c>
+      <c r="D61" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61" t="s">
+        <v>456</v>
+      </c>
+      <c r="F61" t="s">
+        <v>336</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>458</v>
+      </c>
+      <c r="B62" t="s">
+        <v>459</v>
+      </c>
+      <c r="C62" t="s">
+        <v>171</v>
+      </c>
+      <c r="D62" t="s">
+        <v>165</v>
+      </c>
+      <c r="E62" t="s">
+        <v>460</v>
+      </c>
+      <c r="F62" t="s">
+        <v>207</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>462</v>
+      </c>
+      <c r="B63" t="s">
+        <v>463</v>
+      </c>
+      <c r="C63" t="s">
+        <v>164</v>
+      </c>
+      <c r="D63" t="s">
+        <v>165</v>
+      </c>
+      <c r="E63" t="s">
+        <v>464</v>
+      </c>
+      <c r="F63" t="s">
+        <v>465</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>467</v>
+      </c>
+      <c r="B64" t="s">
+        <v>176</v>
+      </c>
+      <c r="C64" t="s">
+        <v>233</v>
+      </c>
+      <c r="D64" t="s">
+        <v>165</v>
+      </c>
+      <c r="E64" t="s">
+        <v>319</v>
+      </c>
+      <c r="F64" t="s">
+        <v>468</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>467</v>
+      </c>
+      <c r="B65" t="s">
+        <v>176</v>
+      </c>
+      <c r="C65" t="s">
+        <v>177</v>
+      </c>
+      <c r="D65" t="s">
+        <v>165</v>
+      </c>
+      <c r="E65" t="s">
+        <v>319</v>
+      </c>
+      <c r="F65" t="s">
+        <v>468</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>467</v>
+      </c>
+      <c r="B66" t="s">
+        <v>176</v>
+      </c>
+      <c r="C66" t="s">
+        <v>217</v>
+      </c>
+      <c r="D66" t="s">
+        <v>165</v>
+      </c>
+      <c r="E66" t="s">
+        <v>319</v>
+      </c>
+      <c r="F66" t="s">
+        <v>468</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>472</v>
+      </c>
+      <c r="B67" t="s">
+        <v>473</v>
+      </c>
+      <c r="C67" t="s">
+        <v>474</v>
+      </c>
+      <c r="D67" t="s">
+        <v>165</v>
+      </c>
+      <c r="E67" t="s">
+        <v>475</v>
+      </c>
+      <c r="F67" t="s">
+        <v>476</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>478</v>
+      </c>
+      <c r="B68" t="s">
+        <v>333</v>
+      </c>
+      <c r="C68" t="s">
+        <v>455</v>
+      </c>
+      <c r="D68" t="s">
+        <v>165</v>
+      </c>
+      <c r="E68" t="s">
+        <v>479</v>
+      </c>
+      <c r="F68" t="s">
+        <v>336</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>481</v>
+      </c>
+      <c r="B69" t="s">
+        <v>482</v>
+      </c>
+      <c r="C69" t="s">
+        <v>483</v>
+      </c>
+      <c r="D69" t="s">
+        <v>165</v>
+      </c>
+      <c r="E69" t="s">
+        <v>195</v>
+      </c>
+      <c r="F69" t="s">
+        <v>314</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>485</v>
+      </c>
+      <c r="B70" t="s">
+        <v>486</v>
+      </c>
+      <c r="C70" t="s">
+        <v>217</v>
+      </c>
+      <c r="D70" t="s">
+        <v>487</v>
+      </c>
+      <c r="E70" t="s">
+        <v>488</v>
+      </c>
+      <c r="F70" t="s">
+        <v>489</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>491</v>
+      </c>
+      <c r="B71" t="s">
+        <v>492</v>
+      </c>
+      <c r="C71" t="s">
+        <v>493</v>
+      </c>
+      <c r="D71" t="s">
+        <v>165</v>
+      </c>
+      <c r="E71" t="s">
+        <v>494</v>
+      </c>
+      <c r="F71" t="s">
+        <v>495</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>491</v>
+      </c>
+      <c r="B72" t="s">
+        <v>492</v>
+      </c>
+      <c r="C72" t="s">
+        <v>497</v>
+      </c>
+      <c r="D72" t="s">
+        <v>165</v>
+      </c>
+      <c r="E72" t="s">
+        <v>494</v>
+      </c>
+      <c r="F72" t="s">
+        <v>495</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>491</v>
+      </c>
+      <c r="B73" t="s">
+        <v>492</v>
+      </c>
+      <c r="C73" t="s">
+        <v>499</v>
+      </c>
+      <c r="D73" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73" t="s">
+        <v>494</v>
+      </c>
+      <c r="F73" t="s">
+        <v>495</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>491</v>
+      </c>
+      <c r="B74" t="s">
+        <v>492</v>
+      </c>
+      <c r="C74" t="s">
+        <v>501</v>
+      </c>
+      <c r="D74" t="s">
+        <v>165</v>
+      </c>
+      <c r="E74" t="s">
+        <v>494</v>
+      </c>
+      <c r="F74" t="s">
+        <v>495</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>491</v>
+      </c>
+      <c r="B75" t="s">
+        <v>492</v>
+      </c>
+      <c r="C75" t="s">
+        <v>503</v>
+      </c>
+      <c r="D75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" t="s">
+        <v>494</v>
+      </c>
+      <c r="F75" t="s">
+        <v>495</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>491</v>
+      </c>
+      <c r="B76" t="s">
+        <v>492</v>
+      </c>
+      <c r="C76" t="s">
+        <v>505</v>
+      </c>
+      <c r="D76" t="s">
+        <v>165</v>
+      </c>
+      <c r="E76" t="s">
+        <v>494</v>
+      </c>
+      <c r="F76" t="s">
+        <v>495</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>491</v>
+      </c>
+      <c r="B77" t="s">
+        <v>492</v>
+      </c>
+      <c r="C77" t="s">
+        <v>507</v>
+      </c>
+      <c r="D77" t="s">
+        <v>165</v>
+      </c>
+      <c r="E77" t="s">
+        <v>494</v>
+      </c>
+      <c r="F77" t="s">
+        <v>495</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>509</v>
+      </c>
+      <c r="B78" t="s">
+        <v>227</v>
+      </c>
+      <c r="C78" t="s">
+        <v>164</v>
+      </c>
+      <c r="D78" t="s">
+        <v>165</v>
+      </c>
+      <c r="E78" t="s">
+        <v>44</v>
+      </c>
+      <c r="F78" t="s">
+        <v>510</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>512</v>
+      </c>
+      <c r="B79" t="s">
+        <v>513</v>
+      </c>
+      <c r="C79" t="s">
+        <v>171</v>
+      </c>
+      <c r="D79" t="s">
+        <v>165</v>
+      </c>
+      <c r="E79" t="s">
+        <v>514</v>
+      </c>
+      <c r="F79" t="s">
+        <v>515</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>517</v>
+      </c>
+      <c r="B80" t="s">
+        <v>518</v>
+      </c>
+      <c r="C80" t="s">
+        <v>519</v>
+      </c>
+      <c r="D80" t="s">
+        <v>165</v>
+      </c>
+      <c r="E80" t="s">
+        <v>520</v>
+      </c>
+      <c r="F80" t="s">
+        <v>521</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>523</v>
+      </c>
+      <c r="B81" t="s">
+        <v>356</v>
+      </c>
+      <c r="C81" t="s">
+        <v>357</v>
+      </c>
+      <c r="D81" t="s">
+        <v>165</v>
+      </c>
+      <c r="E81" t="s">
+        <v>524</v>
+      </c>
+      <c r="F81" t="s">
+        <v>359</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>526</v>
+      </c>
+      <c r="B82" t="s">
+        <v>527</v>
+      </c>
+      <c r="C82" t="s">
+        <v>164</v>
+      </c>
+      <c r="D82" t="s">
+        <v>165</v>
+      </c>
+      <c r="E82" t="s">
+        <v>528</v>
+      </c>
+      <c r="F82" t="s">
+        <v>529</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>531</v>
+      </c>
+      <c r="B83" t="s">
+        <v>532</v>
+      </c>
+      <c r="C83" t="s">
+        <v>164</v>
+      </c>
+      <c r="D83" t="s">
+        <v>165</v>
+      </c>
+      <c r="E83" t="s">
+        <v>533</v>
+      </c>
+      <c r="F83" t="s">
+        <v>405</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>535</v>
+      </c>
+      <c r="B84" t="s">
+        <v>536</v>
+      </c>
+      <c r="C84" t="s">
+        <v>537</v>
+      </c>
+      <c r="D84" t="s">
+        <v>165</v>
+      </c>
+      <c r="E84" t="s">
+        <v>538</v>
+      </c>
+      <c r="F84" t="s">
+        <v>539</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>541</v>
+      </c>
+      <c r="B85" t="s">
+        <v>542</v>
+      </c>
+      <c r="C85" t="s">
+        <v>543</v>
+      </c>
+      <c r="D85" t="s">
+        <v>422</v>
+      </c>
+      <c r="E85" t="s">
+        <v>44</v>
+      </c>
+      <c r="F85" t="s">
+        <v>544</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>546</v>
+      </c>
+      <c r="B86" t="s">
+        <v>547</v>
+      </c>
+      <c r="C86" t="s">
+        <v>307</v>
+      </c>
+      <c r="D86" t="s">
+        <v>184</v>
+      </c>
+      <c r="E86" t="s">
+        <v>548</v>
+      </c>
+      <c r="F86" t="s">
+        <v>186</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>549</v>
       </c>
     </row>
   </sheetData>
@@ -789,6 +4798,85 @@
     <hyperlink ref="H5" r:id="rId4"/>
     <hyperlink ref="H6" r:id="rId5"/>
     <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-11.xlsx
+++ b/docs/xlsx/jobs-2026-09-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="902">
   <si>
     <t>Title</t>
   </si>
@@ -523,15 +523,108 @@
     <t>https://www.idealist.org/en/nonprofit-job/8d369e01137244348d47ee8f1bd97739-account-manager-fire-fighter-partnerships-muscular-dystrophy-association-chicago</t>
   </si>
   <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Springwell, Inc.</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 25.64 - 25.64/hour</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3543d3eeffd4f5597aa64a3bcf37bf2-administrative-assistant-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Administrative Associate &amp; Assistant Creative Writing Instructor</t>
+  </si>
+  <si>
+    <t>Writopia Lab</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cccfdc61b8a74793bf221cc39ea145fa-administrative-associate-assistant-creative-writing-instructor-writopia-lab-washington</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator, CCN</t>
+  </si>
+  <si>
+    <t>Simons Foundation</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c55e28935d1a47f0814e7b04838a6c72-administrative-coordinator-ccn-simons-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90125.00 - 134513.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/ebf6d8e783f245ea84dc44b4bc5ace8c-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Assistant Director for Summer on the Cuyahoga</t>
+  </si>
+  <si>
+    <t>Summer on the Cuyahoga</t>
+  </si>
+  <si>
+    <t>Cleveland, Ohio</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 34000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78770324c2ed43bb9a66bf5000c6462b-assistant-director-for-summer-on-the-cuyahoga-summer-on-the-cuyahoga-cleveland</t>
+  </si>
+  <si>
+    <t>Assisted Living Ombudsman Program Manager</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/adc97c17c0ac43129b072ab8bef921d0-assisted-living-ombudsman-program-manager-springwell-inc-waltham</t>
+  </si>
+  <si>
     <t>Associate Director, Campaign Strategy</t>
   </si>
   <si>
     <t>Playwrights Horizons</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 100000.00/year</t>
   </si>
   <si>
@@ -559,6 +652,111 @@
     <t>https://www.idealist.org/en/nonprofit-job/49234d48438f4551bca02fc0125ccf8c-associate-director-the-housing-lab-impact-justice-oakland</t>
   </si>
   <si>
+    <t>Billing Specialist</t>
+  </si>
+  <si>
+    <t>USD 28.21 - 28.21/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df7b12bc8e9b4208a2630462fadced62-billing-specialist-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Business Manager</t>
+  </si>
+  <si>
+    <t>Friends of the Wissahickon</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Sports Recreation, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a9870a8e1c73465e861119b8985ad0d9-business-manager-friends-of-the-wissahickon-philadelphia</t>
+  </si>
+  <si>
+    <t>Campaign Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 44450.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e353274fb6c341cfb5c33d8f3bc8ec53-campaign-associate-environment-america-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c84f5dd7456643de82a8cf96a8a54876-campaign-associate-environment-america-boston</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2700766efff04bcca81210d77dd196e7-campaign-associate-environment-america-chicago</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>Marlborough, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fbbfd27f2ca144c38fb0fd79baa35a6c-case-manager-springwell-inc-marlborough</t>
+  </si>
+  <si>
+    <t>Case Manager, Guardianship Services</t>
+  </si>
+  <si>
+    <t>Project Guardianship</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Disability, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8edb2e1f89164f5cb4a9a9c84832a81d-case-manager-guardianship-services-project-guardianship-new-york</t>
+  </si>
+  <si>
+    <t>Client Experience Specialist</t>
+  </si>
+  <si>
+    <t>Atticus</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/444bd6b1cd1940f18118219cdd3ec43b-client-experience-specialist-atticus-los-angeles</t>
+  </si>
+  <si>
+    <t>Climate Data Analyst</t>
+  </si>
+  <si>
+    <t>Environmental Investigation Agency - Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da09ad352d16424f90c644b6054a2ed1-climate-data-analyst-environmental-investigation-agency-washington-dc-washington</t>
+  </si>
+  <si>
     <t>Communications &amp; Content Associate (leave replacement)</t>
   </si>
   <si>
@@ -610,6 +808,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/ea1ccfc4650747079e96dd353f2a6f2d-communications-manager-association-for-neighborhood-and-housing-development-new-york</t>
   </si>
   <si>
+    <t>LEAP-NYC</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be0596e4e9ee437ea12a2f5d5bf6d31b-communications-manager-leap-nyc-new-york</t>
+  </si>
+  <si>
     <t>Communications Specialist</t>
   </si>
   <si>
@@ -625,6 +835,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/22d5fba17b9442998512234754dc48de-communications-specialist-new-american-leaders-new-york</t>
   </si>
   <si>
+    <t>Community and Culture Coordinator</t>
+  </si>
+  <si>
+    <t>High Mountain Institute</t>
+  </si>
+  <si>
+    <t>Leadville, Colorado</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8d136ddb3564dd99e1a4758d952f267-community-and-culture-coordinator-high-mountain-institute-leadville</t>
+  </si>
+  <si>
     <t>Community Health Nurse</t>
   </si>
   <si>
@@ -643,6 +868,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/d2d1123f13e7430dbb7888dcd910502a-community-health-nurse-neighborhood-house-tukwila</t>
   </si>
   <si>
+    <t>Compliance Coordinator and Operations Administrator</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Florida</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 90200.00 - 110500.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e8b6a033de9344cb83d868f7e5752881-compliance-coordinator-and-operations-administrator-american-civil-liberties-union-of-florida-miami</t>
+  </si>
+  <si>
+    <t>Conservation Advocate</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e738fb3ddef04466b2c656fafb7b661a-conservation-advocate-environment-america-raleigh</t>
+  </si>
+  <si>
+    <t>Consumer Advocacy Associate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bce76168030d49ca8912071d7421eabe-consumer-advocacy-associate-us-pirg-washington</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9cda299790c7457b84c90dc08a2688f3-consumer-advocacy-associate-us-pirg-portland</t>
+  </si>
+  <si>
     <t>Content Specialist (Castle Hill YMCA)</t>
   </si>
   <si>
@@ -652,24 +925,33 @@
     <t>Bronx County, New York</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 32.00 - 32.00/hour</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4ea4e6f76d58473f874e0d29b52cf5f6-content-specialist-castle-hill-ymca-ymca-of-greater-new-york-bronx-county</t>
   </si>
   <si>
+    <t>Day Program and Employment Services Coordinator</t>
+  </si>
+  <si>
+    <t>Toolworks</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 75500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/042a1a593aee450b97736d54dda20c8a-day-program-and-employment-services-coordinator-toolworks-berkeley</t>
+  </si>
+  <si>
     <t>Deputy Director of Individual Giving</t>
   </si>
   <si>
     <t>Center on Budget and Policy Priorities</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 105000.00 - 135000.00/year</t>
   </si>
   <si>
@@ -688,9 +970,6 @@
     <t>USD 196369.00 - 196369.00/year</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/3c2af32359fd44339def907df6415782-deputy-director-support-transition-american-civil-liberties-union-new-york</t>
   </si>
   <si>
@@ -700,15 +979,24 @@
     <t>Outright International</t>
   </si>
   <si>
-    <t>USD 70000.00 - 70000.00/year</t>
-  </si>
-  <si>
     <t>Conflict Resolution, Human Rights Civil Liberties, Lgbtq</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/330ff7fcea944b828cd996717149745f-development-assistant-outright-international-new-york</t>
   </si>
   <si>
+    <t>Development Associate - Governement Relations</t>
+  </si>
+  <si>
+    <t>Access Living of Metropolitan Chicago</t>
+  </si>
+  <si>
+    <t>USD 61000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f11bc518278746f39c959b85182c8e57-development-associate-governement-relations-access-living-of-metropolitan-chicago-chicago</t>
+  </si>
+  <si>
     <t>Development Coordinator - Los Angeles-based Cat Rescue</t>
   </si>
   <si>
@@ -763,6 +1051,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/0d93db5c818540519d9cade565b9d964-development-director-innocence-justice-louisiana-new-orleans</t>
   </si>
   <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>National Nordic Museum</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db43ddd7e0b942e1b1afb94f2d7f5feb-development-manager-national-nordic-museum-seattle</t>
+  </si>
+  <si>
+    <t>Development Project Manager, Research &amp; Major Gifts</t>
+  </si>
+  <si>
+    <t>Window to the World Communications, Inc. (WTTW/WFMT)</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e7edd45a00642ab94bde6d313432bcb-development-project-manager-research-major-gifts-window-to-the-world-communications-inc-wttwwfmt-chicago</t>
+  </si>
+  <si>
+    <t>Digital Officer</t>
+  </si>
+  <si>
+    <t>Girl Scout Council of the Nation's Capital</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6488977409e4ab5a5e6eee6f2d6fb7c-digital-officer-girl-scout-council-of-the-nations-capital-washington</t>
+  </si>
+  <si>
     <t>Director - Film, Culture &amp; Community</t>
   </si>
   <si>
@@ -808,6 +1141,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/51bafbb504f44deebe7f3c7966a5d726-director-of-development-one-to-world-new-york</t>
   </si>
   <si>
+    <t>Empire Justice Center</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 108702.00 - 113879.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2f5c9993a454edf86d1299c4d333d48-director-of-development-empire-justice-center-albany</t>
+  </si>
+  <si>
     <t>Director of Digital Communications</t>
   </si>
   <si>
@@ -823,6 +1171,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/2e9fd3db084d4262a0928f51e5992172-director-of-digital-communications-guttmacher-institute-new-york</t>
   </si>
   <si>
+    <t>Director of Equity and Culture</t>
+  </si>
+  <si>
+    <t>Remote (Florida)</t>
+  </si>
+  <si>
+    <t>USD 128600.00 - 160700.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfc98de019194fa19fa08dceb187866b-director-of-equity-and-culture-american-civil-liberties-union-of-florida-miami</t>
+  </si>
+  <si>
     <t>Director of Finance &amp; Operations</t>
   </si>
   <si>
@@ -874,6 +1234,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/74a79764d0704a94846b8397413a35ae-director-of-human-resources-the-childrens-home-society-of-new-jersey-trenton</t>
   </si>
   <si>
+    <t>Director of People and Culture</t>
+  </si>
+  <si>
+    <t>Galvanize USA</t>
+  </si>
+  <si>
+    <t>USD 128000.00 - 132000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2a2e32af87847039b67a5e2b1ce2f2b-director-of-people-and-culture-galvanize-usa-washington</t>
+  </si>
+  <si>
+    <t>Director of STEM Education</t>
+  </si>
+  <si>
+    <t>Solar One</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/edc73d6a389b48a7931a7a11f0e0392a-director-of-stem-education-solar-one-new-york</t>
+  </si>
+  <si>
     <t>Director of Technology and Data</t>
   </si>
   <si>
@@ -907,15 +1294,9 @@
     <t>Open Space Institute</t>
   </si>
   <si>
-    <t>Albany, New York</t>
-  </si>
-  <si>
     <t>USD 140000.00 - 190000.00/year</t>
   </si>
   <si>
-    <t>Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/cd8a4bbcbaca4ac4ac8d31ea70865f68-director-or-senior-director-of-government-relations-new-york-state-open-space-institute-albany</t>
   </si>
   <si>
@@ -934,12 +1315,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/85d38a308f444c90add162e318e186f0-director-communications-climate-energy-program-third-way-washington</t>
   </si>
   <si>
+    <t>Director, Raising Child Care Fund</t>
+  </si>
+  <si>
+    <t>Early Childhood Funders Collaborative</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bdb0371116194828a761598538292d67-director-raising-child-care-fund-early-childhood-funders-collaborative-boston</t>
+  </si>
+  <si>
+    <t>Division Chief</t>
+  </si>
+  <si>
+    <t>USD 147202.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/509296449dc6462290abc1a3d61e832d-division-chief-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>DRC Program Officer</t>
+  </si>
+  <si>
+    <t>The Fund for Global Human Rights</t>
+  </si>
+  <si>
+    <t>Remote (Southeast, (no state), CD)</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f5bb62d763c4041b52cc898db5a5ada-drc-program-officer-the-fund-for-global-human-rights-southeast</t>
+  </si>
+  <si>
     <t>English for New Bostonians: Director of Institutional Giving</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 90000.00 - 110000.00/year</t>
   </si>
   <si>
@@ -949,6 +1366,108 @@
     <t>https://www.idealist.org/en/consultant-job/9d54a5166c5648dbb06cc3b2cfa631b4-english-for-new-bostonians-director-of-institutional-giving-boston</t>
   </si>
   <si>
+    <t>Environment New Jersey Campaign Associate</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f11151e140424a7fa677ad34a8888976-environment-new-jersey-campaign-associate-environment-america-philadelphia</t>
+  </si>
+  <si>
+    <t>Environmental Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fcc01a59947941319135a79bcb912916-environmental-organizer-student-pirgs-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db021333449d40c689204a7cda718979-environmental-organizer-student-pirgs-seattle</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d47216a694f542408af561a01219d932-environmental-organizer-student-pirgs-atlanta</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be5eb23bc70244e4957409b8fbf66d35-environmental-organizer-student-pirgs-los-angeles</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4ddd43f21e141768e7a6fccdcf585de-environmental-organizer-student-pirgs-san-diego</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a2568087c7b403b952f237168acf5ba-environmental-organizer-student-pirgs-raleigh</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/985a22c069af4fbda4f94fbbaaab95ed-environmental-organizer-student-pirgs-chicago</t>
+  </si>
+  <si>
+    <t>New Brunswick, New Jersey</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e0cb42859ae4a5fb0a1eaac93fe8e6c-environmental-organizer-student-pirgs-new-brunswick</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b89433238c547c8bb77bfadc0cedddd-environmental-organizer-student-pirgs-austin</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d85cc66ff9745848ab749dfac945d29-environmental-organizer-student-pirgs-philadelphia</t>
+  </si>
+  <si>
+    <t>Lowell, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/655b00a348214458b76cf88624e13735-environmental-organizer-student-pirgs-lowell</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f7307d0cff143aeb72ff19fca77e41a-environmental-organizer-student-pirgs-berkeley</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40daf62de99445c4b626eed85ff4787c-environmental-organizer-student-pirgs-portland</t>
+  </si>
+  <si>
+    <t>Camden, New Jersey</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a5e9dfd430d425ca266246cd6159939-environmental-organizer-student-pirgs-camden</t>
+  </si>
+  <si>
+    <t>Eugene, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28755e8db4a5416c8ade66ea7a43c8a2-environmental-organizer-student-pirgs-eugene</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a9881d3007f402284752393f998ca24-environmental-organizer-student-pirgs-boston</t>
+  </si>
+  <si>
+    <t>Events and Sponsorships Director</t>
+  </si>
+  <si>
+    <t>Les Turner ALS Foundation</t>
+  </si>
+  <si>
+    <t>Skokie, Illinois</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c893167b59e94e9d9591ed7086df2075-events-and-sponsorships-director-les-turner-als-foundation-skokie</t>
+  </si>
+  <si>
     <t>Executive Assistant</t>
   </si>
   <si>
@@ -997,6 +1516,21 @@
     <t>https://www.idealist.org/en/job/1038f006d8a140f298a368d0f652c6e9-executive-director-florida-rights-restoration-coalition-orlando</t>
   </si>
   <si>
+    <t>Executive Office Assistant</t>
+  </si>
+  <si>
+    <t>USD 61240.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/952675239da74bd38c17a91cd71c767f-executive-office-assistant-american-civil-liberties-union-of-florida-miami</t>
+  </si>
+  <si>
+    <t>Executive Program Assistant</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aaebfb731d17466b8eea6bd41a250edf-executive-program-assistant-american-civil-liberties-union-of-florida-miami</t>
+  </si>
+  <si>
     <t>Facilitador/a Niño y Niña - Filial Mendoza</t>
   </si>
   <si>
@@ -1081,6 +1615,78 @@
     <t>https://www.idealist.org/en/nonprofit-job/fb1e0dcdd7784d2c8e5389ba9af30081-financial-manager-northwest-center-for-alternatives-to-pesticides-eugene</t>
   </si>
   <si>
+    <t>Flex Staffing - Program Coordinator - Part-time ($20/hr-$22/hr)</t>
+  </si>
+  <si>
+    <t>Community Services Foundation</t>
+  </si>
+  <si>
+    <t>Glenarden, Maryland</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47f9a4c404864bafa68735af59c492e5-flex-staffing-program-coordinator-part-time-20hr-22hr-community-services-foundation-glenarden</t>
+  </si>
+  <si>
+    <t>Founding Executive Director</t>
+  </si>
+  <si>
+    <t>Mighty Consulting</t>
+  </si>
+  <si>
+    <t>USD 137000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2093494989f34dc9bdbedbac3a8356d0-founding-executive-director-mighty-consulting-saint-paul</t>
+  </si>
+  <si>
+    <t>Fractional Fundraising and Development Consultant</t>
+  </si>
+  <si>
+    <t>Little Oaks Center for Neurodevelopment</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb4e3cfc6bd24061b974b67349e7dbf8-fractional-fundraising-and-development-consultant-little-oaks-center-for-neurodevelopment-new-york</t>
+  </si>
+  <si>
+    <t>Fundraising Event Manager</t>
+  </si>
+  <si>
+    <t>Sarcoma Foundation of America</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>Health Medicine, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/061d0d16e636469d81f0bb7d8cdc0195-fundraising-event-manager-sarcoma-foundation-of-america-bethesda</t>
+  </si>
+  <si>
+    <t>Geriatric Support Services Coordinator</t>
+  </si>
+  <si>
+    <t>Disability, Seniors Retirement, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d1bc4ea1e334fe384b17befc851ee8a-geriatric-support-services-coordinator-springwell-inc-marlborough</t>
+  </si>
+  <si>
     <t>Global Fundraising Director</t>
   </si>
   <si>
@@ -1099,6 +1705,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/c3632210ea584097979f8bf31d5340a7-global-fundraising-director-the-salvation-army-national-headquarters-alexandria</t>
   </si>
   <si>
+    <t>Global Social Media &amp; Community Manager</t>
+  </si>
+  <si>
+    <t>Technovation</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98b774ffd7d14b9fb63965a78a8d745c-global-social-media-community-manager-technovation-menlo-park</t>
+  </si>
+  <si>
+    <t>Grant Accountant</t>
+  </si>
+  <si>
+    <t>USD 66300.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/56004c47e3d34cf997bc211139b742ad-grant-accountant-leap-nyc-new-york</t>
+  </si>
+  <si>
     <t>Grants &amp; Contracts Associate</t>
   </si>
   <si>
@@ -1114,6 +1741,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/b5432278d2884e66a798118314c6bb45-grants-contracts-associate-great-plains-institute-minneapolis</t>
   </si>
   <si>
+    <t>Grants Officer</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8211fe833fca49babdfe56c5b397a31c-grants-officer-girl-scout-council-of-the-nations-capital-washington</t>
+  </si>
+  <si>
     <t>Head of Revenue Operations</t>
   </si>
   <si>
@@ -1123,6 +1756,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/4b874260b6494883a76e3d50dad402b9-head-of-revenue-operations-find-calabar</t>
   </si>
   <si>
+    <t>High School Mentor</t>
+  </si>
+  <si>
+    <t>Summer Search</t>
+  </si>
+  <si>
+    <t>USD 30.06 - 32.99/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3263649e5214a55a8ec19fa0bc3877f-high-school-mentor-summer-search-tukwila</t>
+  </si>
+  <si>
     <t>Hiring Manager</t>
   </si>
   <si>
@@ -1144,6 +1789,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/0ce57783442e4f3aa49e2d4dcf825675-human-resource-manager-american-association-of-state-highway-transportation-officials-washington</t>
   </si>
   <si>
+    <t>Information &amp; Referral Specialist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8186a624a9014685b8a4bfbd9dc3ed04-information-referral-specialist-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Intake Assessor</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c2e90afe50748c6993ff88ec24636be-intake-assessor-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Lead Staff Attorney Medical-Financial-Legal Partnership</t>
+  </si>
+  <si>
+    <t>Tzedek DC</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 119000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49a152cf468d437c87f5d98549ce20c0-lead-staff-attorney-medical-financial-legal-partnership-tzedek-dc-washington</t>
+  </si>
+  <si>
     <t>Legal Content Director</t>
   </si>
   <si>
@@ -1186,6 +1858,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7077ce228b354c70aef07e96205c4ec1-legal-justice-advocate-womens-community-center-brattleboro</t>
   </si>
   <si>
+    <t>Legislative Director, California</t>
+  </si>
+  <si>
+    <t>Common Cause Education Fund</t>
+  </si>
+  <si>
+    <t>USD 100786.00 - 116699.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/415d3edf72c5452891aaf82c1eb4f5e2-legislative-director-california-common-cause-education-fund-washington</t>
+  </si>
+  <si>
     <t>Local Food Access Warehouse Packer</t>
   </si>
   <si>
@@ -1222,6 +1909,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/7fd4feb53f6b468cbd9b07d7e6bcfb7e-logistics-resources-manager-beth-el-farm-worker-ministry-inc-wimauma</t>
   </si>
   <si>
+    <t>Manager of Market Access Partnerships - Contractor</t>
+  </si>
+  <si>
+    <t>Nest Inc.</t>
+  </si>
+  <si>
+    <t>USD 3000.00 - 3000.00/month</t>
+  </si>
+  <si>
+    <t>Arts Music, Economic Development, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc4358ebdc9c4cf185bf4862263c59a9-manager-of-market-access-partnerships-contractor-nest-inc-new-york</t>
+  </si>
+  <si>
+    <t>Manager, Donor Relations</t>
+  </si>
+  <si>
+    <t>Brady United Against Gun Violence</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4628340dd63c4f388c97f1846d83d180-manager-donor-relations-brady-united-against-gun-violence-washington</t>
+  </si>
+  <si>
+    <t>Manager, Office of the Vice President for Institutional Advancement</t>
+  </si>
+  <si>
+    <t>Teachers College, Columbia University</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7189386608dc4990adac4b13d1db0454-manager-office-of-the-vice-president-for-institutional-advancement-teachers-college-columbia-university-new-york</t>
+  </si>
+  <si>
     <t>Manager, Programs and Grants</t>
   </si>
   <si>
@@ -1231,9 +1960,6 @@
     <t>USD 55000.00 - 60000.00/year</t>
   </si>
   <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/58e648c8ba584c40a9f537d0f3b0e599-manager-programs-and-grants-northeast-business-group-on-health-new-york</t>
   </si>
   <si>
@@ -1282,9 +2008,6 @@
     <t>The Funding Studio</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 30.00 - 30.00/hour</t>
   </si>
   <si>
@@ -1294,6 +2017,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/f8d8d146165943cb9227b3bb22d797cb-nonprofit-operations-specialist-the-funding-studio-phoenix</t>
   </si>
   <si>
+    <t>Nurse Manager (Home Care Setting)</t>
+  </si>
+  <si>
+    <t>Maryknoll Sisters</t>
+  </si>
+  <si>
+    <t>Ossining, New York</t>
+  </si>
+  <si>
+    <t>USD 118560.00 - 118560.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d78dc13937b64678a07eb76b59f4c547-nurse-manager-home-care-setting-maryknoll-sisters-ossining</t>
+  </si>
+  <si>
+    <t>Oceans Advocate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/414ebc4778fb4dcc930b95bec1bc2ccc-oceans-advocate-environment-america-washington</t>
+  </si>
+  <si>
+    <t>Officer, State Decarbonization Campaign Lead</t>
+  </si>
+  <si>
+    <t>Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>USD 121100.00 - 135400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/542f4a6157274f44a036e358a5d6bfb4-officer-state-decarbonization-campaign-lead-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a99769a0538c4ccda64d410f71c887ad-officer-state-decarbonization-campaign-lead-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
+    <t>Operations Assistant</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/609667b749ec4bbc8292b084ee4fd84c-operations-assistant-galvanize-usa-seattle</t>
+  </si>
+  <si>
     <t>Operations Manager</t>
   </si>
   <si>
@@ -1354,9 +2125,6 @@
     <t>Overdose Prevention Specialist</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 30.00 - 32.00/hour</t>
   </si>
   <si>
@@ -1366,6 +2134,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/6f42d28c976047e6b961baefb6b06ab6-overdose-prevention-specialist-the-peoples-harm-reduction-alliance-phra-seattle</t>
   </si>
   <si>
+    <t>Partnerships &amp; Community Manager</t>
+  </si>
+  <si>
+    <t>Parking Reform Network</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Transportation, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57c0fc9fc4ed4afb942e422b36b77dea-partnerships-community-manager-parking-reform-network-portland</t>
+  </si>
+  <si>
     <t>Philanthropic Advisor</t>
   </si>
   <si>
@@ -1378,6 +2161,21 @@
     <t>https://www.idealist.org/en/job/b327c229ff32481992ab855b67432780-philanthropic-advisor-baylor-university-waco</t>
   </si>
   <si>
+    <t>Pike Place Market Foundation Director of Development</t>
+  </si>
+  <si>
+    <t>Clover Search Works</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/b8fc00109a314e70b296851e569d7e8d-pike-place-market-foundation-director-of-development-clover-search-works-seattle</t>
+  </si>
+  <si>
     <t>PRN Residential Master's Level Counselor</t>
   </si>
   <si>
@@ -1408,15 +2206,27 @@
     <t>Everyone On</t>
   </si>
   <si>
-    <t>USD 65000.00 - 65000.00/year</t>
-  </si>
-  <si>
     <t>Community Development, Education, Science Technology</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/dc67906db4254c7685bc256b10af98dc-program-coordinator-everyone-on-los-angeles</t>
   </si>
   <si>
+    <t>Southeastern Regional Action Council</t>
+  </si>
+  <si>
+    <t>Norwich, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1cba789b0d124eaa8f347434d10f3b2d-program-coordinator-southeastern-regional-action-council-norwich</t>
+  </si>
+  <si>
     <t>Program Director, The Menopause Project</t>
   </si>
   <si>
@@ -1432,6 +2242,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/5d7195500b8242b1a83639709c48bdf9-program-director-the-menopause-project-impact-justice-washington</t>
   </si>
   <si>
+    <t>Program Finance Manager</t>
+  </si>
+  <si>
+    <t>Karuna Center for Peacebuilding</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea92f71fdd844daea31acc948f59b2aa-program-finance-manager-karuna-center-for-peacebuilding-greenfield</t>
+  </si>
+  <si>
+    <t>Program Operations Coordinator</t>
+  </si>
+  <si>
+    <t>USD 30.10 - 32.46/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9bccd71a26a04e90b385db94cb9f06cf-program-operations-coordinator-summer-search-tukwila</t>
+  </si>
+  <si>
+    <t>Program Specialist - Community Services ($47k-$49k)</t>
+  </si>
+  <si>
+    <t>USD 47000.00 - 49000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/83e489ba761646a4adc366723121376d-program-specialist-community-services-47k-49k-community-services-foundation-glenarden</t>
+  </si>
+  <si>
+    <t>Public Interest State Advocate</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0bb4831e0b4f4622b1a8414397ce5930-public-interest-state-advocate-us-pirg-austin</t>
+  </si>
+  <si>
     <t>Red Hook on the Road Program Manager</t>
   </si>
   <si>
@@ -1459,6 +2311,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/e6489ba462c04d5a8d45e41fb575d6e4-registered-nurse-youth-villages-douglasville</t>
   </si>
   <si>
+    <t>Registered Nurse (RN)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9be1b1d50cb94a6a87a90a19f6a9c9da-registered-nurse-rn-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Research Administrator</t>
+  </si>
+  <si>
+    <t>The Public Interest Network</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 40250.00 - 42750.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a79788d69a10491ca8320889da8798e3-research-administrator-the-public-interest-network-denver</t>
+  </si>
+  <si>
     <t>Research Analyst - New Organizing SEIU Healthcare Michigan (HCMI)</t>
   </si>
   <si>
@@ -1471,6 +2347,21 @@
     <t>https://www.idealist.org/en/job/045e9b884091495abb49ba012a8651f0-research-analyst-new-organizing-seiu-healthcare-michigan-hcmi-seiu-detroit</t>
   </si>
   <si>
+    <t>Research Fellowship</t>
+  </si>
+  <si>
+    <t>Partners for Public Good</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/545f3c691e28410a97680278a5098ee7-research-fellowship-partners-for-public-good-los-angeles</t>
+  </si>
+  <si>
     <t>Seasonal Food Team Member</t>
   </si>
   <si>
@@ -1543,6 +2434,45 @@
     <t>https://www.idealist.org/en/business-job/29da4338a9b3480ba8120569b2eaec9c-senior-business-development-manager-women-first-digital-lagos</t>
   </si>
   <si>
+    <t>Senior Civil Rights Attorney</t>
+  </si>
+  <si>
+    <t>New York Lawyers for the Public Interest</t>
+  </si>
+  <si>
+    <t>Environment, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7cbfc1c695e244a3b5e6df1fefd95976-senior-civil-rights-attorney-new-york-lawyers-for-the-public-interest-new-york</t>
+  </si>
+  <si>
+    <t>Senior Development Manager</t>
+  </si>
+  <si>
+    <t>Washington STEM</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 101450.00 - 142031.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10a7f014ac2049c5b8617fb7704614a1-senior-development-manager-washington-stem-seattle</t>
+  </si>
+  <si>
+    <t>Senior Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Lambda Legal</t>
+  </si>
+  <si>
+    <t>USD 113891.00 - 153956.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f1d1bc3b3c24d6296a47e8b96d6a7c0-senior-major-gifts-officer-lambda-legal-new-york</t>
+  </si>
+  <si>
     <t>Senior Program Manager - Global Rights and Grantmaking</t>
   </si>
   <si>
@@ -1573,9 +2503,6 @@
     <t>YouthBuild Philadelphia</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>USD 60000.00 - 68000.00/year</t>
   </si>
   <si>
@@ -1585,6 +2512,84 @@
     <t>https://www.idealist.org/en/nonprofit-job/f5fc5fd907c24662aff9c4896e0bff5b-special-education-teacher-immediate-hire-youthbuild-philadelphia-philadelphia</t>
   </si>
   <si>
+    <t>Staff Counsel (Junior Level Position)</t>
+  </si>
+  <si>
+    <t>Crystal Stairs of Los Angeles</t>
+  </si>
+  <si>
+    <t>Ladera Heights, California</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2ded2b9b3c6f408d9afdaa493509e01b-staff-counsel-junior-level-position-crystal-stairs-of-los-angeles-ladera-heights</t>
+  </si>
+  <si>
+    <t>Supervising Attorney (CBEST) – Economic Stability Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>East Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 105174.00 - 127961.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85ef20fd724440b9a968b13ffe287023-supervising-attorney-cbest-economic-stability-workgroup-legal-aid-foundation-of-los-angeles-east-los-angeles</t>
+  </si>
+  <si>
+    <t>Supervising Senior Litigation Attorney</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 113879.00 - 119055.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47a997be32d5408891f5f94db89772c0-supervising-senior-litigation-attorney-empire-justice-center-rochester</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2e820df293b42659f7de47f16d90ee0-supervisor-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Supportive Housing Coordinator - Rapid Re-Housing</t>
+  </si>
+  <si>
+    <t>Homeless Services Network of Central Florida</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2132d7fbf8c447f8b8467341eda2a895-supportive-housing-coordinator-rapid-re-housing-homeless-services-network-of-central-florida-orlando</t>
+  </si>
+  <si>
+    <t>Teaching Faculty Position in Environmental Science, Open Rank</t>
+  </si>
+  <si>
+    <t>Georgetown University</t>
+  </si>
+  <si>
+    <t>Doha, Qatar</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b7d2b009f71c4a5b9171adc10daee873-teaching-faculty-position-in-environmental-science-open-rank-georgetown-university-doha</t>
+  </si>
+  <si>
     <t>Technical Advisor – International Business &amp; Economic Development</t>
   </si>
   <si>
@@ -1594,6 +2599,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/02b7722252ea47f586326879245be204-technical-advisor-international-business-economic-development-the-salvation-army-national-headquarters-alexandria</t>
   </si>
   <si>
+    <t>Temp - Community Manager</t>
+  </si>
+  <si>
+    <t>TIMBY (This is My Backyard)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/564a7e9999a24c048d72f9e01b7e4ffd-temp-community-manager-timby-this-is-my-backyard-montreal</t>
+  </si>
+  <si>
+    <t>Training &amp; Communications Associate: Health Justice</t>
+  </si>
+  <si>
+    <t>The Young Women's Project</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e66f9c7c4cc442588d3ddd86f5761659-training-communications-associate-health-justice-the-young-womens-project-washington</t>
+  </si>
+  <si>
     <t>Vice President of Finance and Administration</t>
   </si>
   <si>
@@ -1639,6 +2668,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/eec2370fbcdc476db7931bca870e8992-vice-president-membership-american-pharmacists-association-washington</t>
   </si>
   <si>
+    <t>Washington (Senior) Policy Manager</t>
+  </si>
+  <si>
+    <t>Renewable Northwest</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0610f770020f48dfb896e67d39c5254b-washington-senior-policy-manager-renewable-northwest-portland</t>
+  </si>
+  <si>
     <t>Workforce Planning and Org Design Consultant</t>
   </si>
   <si>
@@ -1664,6 +2711,15 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/a373435632334efba3f2446b4daf8d35-writing-instructor-minds-matter-boston-boston</t>
+  </si>
+  <si>
+    <t>Zero Waste Campaign Associate</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e873c7f7b0454e0cbf743f2eccc05a39-zero-waste-campaign-associate-us-pirg-los-angeles</t>
   </si>
 </sst>
 </file>
@@ -2795,7 +3851,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2914,53 +3970,53 @@
         <v>183</v>
       </c>
       <c r="D5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" t="s">
         <v>184</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" t="s">
         <v>188</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" t="s">
         <v>189</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="D6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" t="s">
-        <v>191</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" t="s">
         <v>193</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>194</v>
-      </c>
-      <c r="D7" t="s">
-        <v>165</v>
       </c>
       <c r="E7" t="s">
         <v>195</v>
@@ -2977,1816 +4033,4047 @@
         <v>198</v>
       </c>
       <c r="B8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" t="s">
         <v>199</v>
       </c>
-      <c r="C8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="F8" t="s">
-        <v>201</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" t="s">
         <v>203</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
         <v>204</v>
       </c>
-      <c r="C9" t="s">
+      <c r="H9" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="D9" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" t="s">
-        <v>206</v>
-      </c>
-      <c r="F9" t="s">
-        <v>207</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" t="s">
         <v>209</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>210</v>
       </c>
-      <c r="C10" t="s">
+      <c r="H10" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D10" t="s">
-        <v>212</v>
-      </c>
-      <c r="E10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B11" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
         <v>165</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F11" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B12" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C12" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D12" t="s">
         <v>165</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F12" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D13" t="s">
         <v>165</v>
       </c>
       <c r="E13" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B14" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D14" t="s">
         <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F14" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="B15" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="D15" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F15" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B16" t="s">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="D16" t="s">
         <v>165</v>
       </c>
       <c r="E16" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="F16" t="s">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B17" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D17" t="s">
         <v>165</v>
       </c>
       <c r="E17" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="F17" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B18" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D18" t="s">
         <v>165</v>
       </c>
       <c r="E18" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="F18" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="B19" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D19" t="s">
         <v>165</v>
       </c>
       <c r="E19" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="F19" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="B20" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="C20" t="s">
-        <v>164</v>
+        <v>249</v>
       </c>
       <c r="D20" t="s">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="E20" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="F20" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D21" t="s">
         <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>272</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C22" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="D22" t="s">
         <v>165</v>
       </c>
       <c r="E22" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F22" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C23" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D23" t="s">
         <v>165</v>
       </c>
       <c r="E23" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="C24" t="s">
-        <v>283</v>
+        <v>164</v>
       </c>
       <c r="D24" t="s">
         <v>165</v>
       </c>
       <c r="E24" t="s">
-        <v>178</v>
+        <v>270</v>
       </c>
       <c r="F24" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C25" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D25" t="s">
         <v>165</v>
       </c>
       <c r="E25" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="F25" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C26" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D26" t="s">
         <v>165</v>
       </c>
       <c r="E26" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="F26" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="D27" t="s">
         <v>165</v>
       </c>
       <c r="E27" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="F27" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s">
-        <v>302</v>
+        <v>222</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>291</v>
       </c>
       <c r="D28" t="s">
         <v>165</v>
       </c>
       <c r="E28" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="F28" t="s">
-        <v>304</v>
+        <v>224</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>295</v>
       </c>
       <c r="C29" t="s">
-        <v>307</v>
+        <v>177</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
       </c>
       <c r="E29" t="s">
-        <v>308</v>
+        <v>223</v>
       </c>
       <c r="F29" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C30" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="D30" t="s">
         <v>165</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>223</v>
       </c>
       <c r="F30" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="C31" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="E31" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="F31" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="C32" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D32" t="s">
         <v>165</v>
       </c>
       <c r="E32" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="F32" t="s">
-        <v>325</v>
+        <v>44</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="C33" t="s">
-        <v>329</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
         <v>165</v>
       </c>
       <c r="E33" t="s">
-        <v>44</v>
+        <v>312</v>
       </c>
       <c r="F33" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="C34" t="s">
-        <v>334</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s">
         <v>165</v>
       </c>
       <c r="E34" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="F34" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="C35" t="s">
-        <v>339</v>
+        <v>183</v>
       </c>
       <c r="D35" t="s">
         <v>165</v>
       </c>
       <c r="E35" t="s">
-        <v>340</v>
+        <v>265</v>
       </c>
       <c r="F35" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C36" t="s">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="D36" t="s">
         <v>165</v>
       </c>
       <c r="E36" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F36" t="s">
-        <v>336</v>
+        <v>44</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="C37" t="s">
-        <v>164</v>
+        <v>329</v>
       </c>
       <c r="D37" t="s">
         <v>165</v>
       </c>
       <c r="E37" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="F37" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="C38" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="D38" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="E38" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="F38" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="C39" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="D39" t="s">
         <v>165</v>
       </c>
       <c r="E39" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="F39" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="B40" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="C40" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="D40" t="s">
         <v>165</v>
       </c>
       <c r="E40" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="F40" t="s">
-        <v>299</v>
+        <v>204</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="C41" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="D41" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="F41" t="s">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s">
-        <v>189</v>
+        <v>356</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D42" t="s">
         <v>165</v>
       </c>
       <c r="E42" t="s">
-        <v>44</v>
+        <v>357</v>
       </c>
       <c r="F42" t="s">
-        <v>44</v>
+        <v>358</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C43" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="D43" t="s">
         <v>165</v>
       </c>
       <c r="E43" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="F43" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C44" t="s">
-        <v>378</v>
+        <v>183</v>
       </c>
       <c r="D44" t="s">
         <v>165</v>
       </c>
       <c r="E44" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="F44" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s">
-        <v>189</v>
+        <v>371</v>
       </c>
       <c r="C45" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D45" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>372</v>
       </c>
       <c r="F45" t="s">
-        <v>44</v>
+        <v>373</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C46" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D46" t="s">
         <v>165</v>
       </c>
       <c r="E46" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="F46" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C47" t="s">
-        <v>392</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="F47" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s">
-        <v>397</v>
+        <v>285</v>
       </c>
       <c r="C48" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="D48" t="s">
         <v>165</v>
       </c>
       <c r="E48" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="F48" t="s">
-        <v>400</v>
+        <v>288</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="C49" t="s">
-        <v>171</v>
+        <v>391</v>
       </c>
       <c r="D49" t="s">
         <v>165</v>
       </c>
       <c r="E49" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="F49" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="C50" t="s">
         <v>164</v>
       </c>
       <c r="D50" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="E50" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="F50" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C51" t="s">
-        <v>392</v>
+        <v>164</v>
       </c>
       <c r="D51" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="E51" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F51" t="s">
-        <v>394</v>
+        <v>44</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="B52" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="C52" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="D52" t="s">
         <v>165</v>
       </c>
       <c r="E52" t="s">
-        <v>417</v>
+        <v>209</v>
       </c>
       <c r="F52" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="B53" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="C53" t="s">
         <v>164</v>
       </c>
       <c r="D53" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="E53" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="F53" t="s">
-        <v>424</v>
+        <v>44</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="C54" t="s">
-        <v>428</v>
+        <v>183</v>
       </c>
       <c r="D54" t="s">
         <v>165</v>
       </c>
       <c r="E54" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="F54" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="C55" t="s">
-        <v>432</v>
+        <v>403</v>
       </c>
       <c r="D55" t="s">
         <v>165</v>
       </c>
       <c r="E55" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="F55" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C56" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="D56" t="s">
         <v>165</v>
       </c>
       <c r="E56" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F56" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C57" t="s">
-        <v>164</v>
+        <v>376</v>
       </c>
       <c r="D57" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="E57" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="F57" t="s">
-        <v>439</v>
+        <v>224</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s">
-        <v>443</v>
+        <v>177</v>
       </c>
       <c r="D58" t="s">
         <v>165</v>
       </c>
       <c r="E58" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F58" t="s">
-        <v>44</v>
+        <v>431</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C59" t="s">
-        <v>446</v>
+        <v>164</v>
       </c>
       <c r="D59" t="s">
         <v>165</v>
       </c>
       <c r="E59" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="F59" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s">
-        <v>451</v>
+        <v>187</v>
       </c>
       <c r="C60" t="s">
-        <v>452</v>
+        <v>188</v>
       </c>
       <c r="D60" t="s">
         <v>165</v>
       </c>
       <c r="E60" t="s">
-        <v>44</v>
+        <v>439</v>
       </c>
       <c r="F60" t="s">
         <v>44</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s">
-        <v>333</v>
+        <v>442</v>
       </c>
       <c r="C61" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="D61" t="s">
         <v>165</v>
       </c>
       <c r="E61" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F61" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B62" t="s">
-        <v>459</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="D62" t="s">
         <v>165</v>
       </c>
       <c r="E62" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="F62" t="s">
-        <v>207</v>
+        <v>448</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s">
-        <v>463</v>
+        <v>222</v>
       </c>
       <c r="C63" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="D63" t="s">
         <v>165</v>
       </c>
       <c r="E63" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F63" t="s">
-        <v>465</v>
+        <v>224</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s">
-        <v>176</v>
+        <v>454</v>
       </c>
       <c r="C64" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="D64" t="s">
         <v>165</v>
       </c>
       <c r="E64" t="s">
-        <v>319</v>
+        <v>223</v>
       </c>
       <c r="F64" t="s">
-        <v>468</v>
+        <v>224</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="B65" t="s">
-        <v>176</v>
+        <v>454</v>
       </c>
       <c r="C65" t="s">
-        <v>177</v>
+        <v>347</v>
       </c>
       <c r="D65" t="s">
         <v>165</v>
       </c>
       <c r="E65" t="s">
-        <v>319</v>
+        <v>223</v>
       </c>
       <c r="F65" t="s">
-        <v>468</v>
+        <v>224</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s">
-        <v>176</v>
+        <v>454</v>
       </c>
       <c r="C66" t="s">
-        <v>217</v>
+        <v>457</v>
       </c>
       <c r="D66" t="s">
         <v>165</v>
       </c>
       <c r="E66" t="s">
-        <v>319</v>
+        <v>223</v>
       </c>
       <c r="F66" t="s">
-        <v>468</v>
+        <v>224</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="C67" t="s">
-        <v>474</v>
+        <v>329</v>
       </c>
       <c r="D67" t="s">
         <v>165</v>
       </c>
       <c r="E67" t="s">
-        <v>475</v>
+        <v>223</v>
       </c>
       <c r="F67" t="s">
-        <v>476</v>
+        <v>224</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s">
-        <v>333</v>
+        <v>454</v>
       </c>
       <c r="C68" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D68" t="s">
         <v>165</v>
       </c>
       <c r="E68" t="s">
-        <v>479</v>
+        <v>223</v>
       </c>
       <c r="F68" t="s">
-        <v>336</v>
+        <v>224</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="B69" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="C69" t="s">
-        <v>483</v>
+        <v>291</v>
       </c>
       <c r="D69" t="s">
         <v>165</v>
       </c>
       <c r="E69" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="F69" t="s">
-        <v>314</v>
+        <v>224</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="C70" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D70" t="s">
-        <v>487</v>
+        <v>165</v>
       </c>
       <c r="E70" t="s">
-        <v>488</v>
+        <v>223</v>
       </c>
       <c r="F70" t="s">
-        <v>489</v>
+        <v>224</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="B71" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="C71" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="D71" t="s">
         <v>165</v>
       </c>
       <c r="E71" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
       <c r="F71" t="s">
-        <v>495</v>
+        <v>224</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="C72" t="s">
-        <v>497</v>
+        <v>466</v>
       </c>
       <c r="D72" t="s">
         <v>165</v>
       </c>
       <c r="E72" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
       <c r="F72" t="s">
-        <v>495</v>
+        <v>224</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>498</v>
+        <v>467</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="B73" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="C73" t="s">
-        <v>499</v>
+        <v>217</v>
       </c>
       <c r="D73" t="s">
         <v>165</v>
       </c>
       <c r="E73" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
       <c r="F73" t="s">
-        <v>495</v>
+        <v>224</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="B74" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="C74" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="D74" t="s">
         <v>165</v>
       </c>
       <c r="E74" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
       <c r="F74" t="s">
-        <v>495</v>
+        <v>224</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="B75" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="C75" t="s">
-        <v>503</v>
+        <v>307</v>
       </c>
       <c r="D75" t="s">
         <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
       <c r="F75" t="s">
-        <v>495</v>
+        <v>224</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="B76" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="C76" t="s">
-        <v>505</v>
+        <v>298</v>
       </c>
       <c r="D76" t="s">
         <v>165</v>
       </c>
       <c r="E76" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
       <c r="F76" t="s">
-        <v>495</v>
+        <v>224</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>506</v>
+        <v>472</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="B77" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="C77" t="s">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="D77" t="s">
         <v>165</v>
       </c>
       <c r="E77" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
       <c r="F77" t="s">
-        <v>495</v>
+        <v>224</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>508</v>
+        <v>474</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>509</v>
+        <v>453</v>
       </c>
       <c r="B78" t="s">
-        <v>227</v>
+        <v>454</v>
       </c>
       <c r="C78" t="s">
-        <v>164</v>
+        <v>475</v>
       </c>
       <c r="D78" t="s">
         <v>165</v>
       </c>
       <c r="E78" t="s">
-        <v>44</v>
+        <v>223</v>
       </c>
       <c r="F78" t="s">
-        <v>510</v>
+        <v>224</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>511</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s">
-        <v>513</v>
+        <v>454</v>
       </c>
       <c r="C79" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="D79" t="s">
         <v>165</v>
       </c>
       <c r="E79" t="s">
-        <v>514</v>
+        <v>223</v>
       </c>
       <c r="F79" t="s">
-        <v>515</v>
+        <v>224</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>516</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>517</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s">
-        <v>518</v>
+        <v>479</v>
       </c>
       <c r="C80" t="s">
-        <v>519</v>
+        <v>480</v>
       </c>
       <c r="D80" t="s">
         <v>165</v>
       </c>
       <c r="E80" t="s">
-        <v>520</v>
+        <v>481</v>
       </c>
       <c r="F80" t="s">
-        <v>521</v>
+        <v>482</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>522</v>
+        <v>483</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>523</v>
+        <v>484</v>
       </c>
       <c r="B81" t="s">
-        <v>356</v>
+        <v>485</v>
       </c>
       <c r="C81" t="s">
-        <v>357</v>
+        <v>486</v>
       </c>
       <c r="D81" t="s">
         <v>165</v>
       </c>
       <c r="E81" t="s">
-        <v>524</v>
+        <v>44</v>
       </c>
       <c r="F81" t="s">
-        <v>359</v>
+        <v>487</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>525</v>
+        <v>488</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>526</v>
+        <v>489</v>
       </c>
       <c r="B82" t="s">
-        <v>527</v>
+        <v>490</v>
       </c>
       <c r="C82" t="s">
-        <v>164</v>
+        <v>491</v>
       </c>
       <c r="D82" t="s">
         <v>165</v>
       </c>
       <c r="E82" t="s">
-        <v>528</v>
+        <v>492</v>
       </c>
       <c r="F82" t="s">
-        <v>529</v>
+        <v>493</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>530</v>
+        <v>494</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>531</v>
+        <v>489</v>
       </c>
       <c r="B83" t="s">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="C83" t="s">
-        <v>164</v>
+        <v>496</v>
       </c>
       <c r="D83" t="s">
         <v>165</v>
       </c>
       <c r="E83" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="F83" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>535</v>
+        <v>500</v>
       </c>
       <c r="B84" t="s">
-        <v>536</v>
+        <v>285</v>
       </c>
       <c r="C84" t="s">
-        <v>537</v>
+        <v>286</v>
       </c>
       <c r="D84" t="s">
         <v>165</v>
       </c>
       <c r="E84" t="s">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="F84" t="s">
-        <v>539</v>
+        <v>288</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>540</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>541</v>
+        <v>503</v>
       </c>
       <c r="B85" t="s">
-        <v>542</v>
+        <v>285</v>
       </c>
       <c r="C85" t="s">
-        <v>543</v>
+        <v>286</v>
       </c>
       <c r="D85" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>501</v>
       </c>
       <c r="F85" t="s">
-        <v>544</v>
+        <v>288</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>545</v>
+        <v>504</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>505</v>
+      </c>
+      <c r="B86" t="s">
+        <v>506</v>
+      </c>
+      <c r="C86" t="s">
+        <v>507</v>
+      </c>
+      <c r="D86" t="s">
+        <v>165</v>
+      </c>
+      <c r="E86" t="s">
+        <v>44</v>
+      </c>
+      <c r="F86" t="s">
+        <v>508</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>510</v>
+      </c>
+      <c r="B87" t="s">
+        <v>511</v>
+      </c>
+      <c r="C87" t="s">
+        <v>512</v>
+      </c>
+      <c r="D87" t="s">
+        <v>165</v>
+      </c>
+      <c r="E87" t="s">
+        <v>513</v>
+      </c>
+      <c r="F87" t="s">
+        <v>514</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>516</v>
+      </c>
+      <c r="B88" t="s">
+        <v>511</v>
+      </c>
+      <c r="C88" t="s">
+        <v>517</v>
+      </c>
+      <c r="D88" t="s">
+        <v>165</v>
+      </c>
+      <c r="E88" t="s">
+        <v>518</v>
+      </c>
+      <c r="F88" t="s">
+        <v>514</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>520</v>
+      </c>
+      <c r="B89" t="s">
+        <v>511</v>
+      </c>
+      <c r="C89" t="s">
+        <v>521</v>
+      </c>
+      <c r="D89" t="s">
+        <v>165</v>
+      </c>
+      <c r="E89" t="s">
+        <v>513</v>
+      </c>
+      <c r="F89" t="s">
+        <v>514</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>523</v>
+      </c>
+      <c r="B90" t="s">
+        <v>524</v>
+      </c>
+      <c r="C90" t="s">
+        <v>164</v>
+      </c>
+      <c r="D90" t="s">
+        <v>165</v>
+      </c>
+      <c r="E90" t="s">
+        <v>525</v>
+      </c>
+      <c r="F90" t="s">
+        <v>526</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>528</v>
+      </c>
+      <c r="B91" t="s">
+        <v>529</v>
+      </c>
+      <c r="C91" t="s">
+        <v>530</v>
+      </c>
+      <c r="D91" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91" t="s">
+        <v>531</v>
+      </c>
+      <c r="F91" t="s">
+        <v>224</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>533</v>
+      </c>
+      <c r="B92" t="s">
+        <v>534</v>
+      </c>
+      <c r="C92" t="s">
+        <v>535</v>
+      </c>
+      <c r="D92" t="s">
+        <v>194</v>
+      </c>
+      <c r="E92" t="s">
+        <v>536</v>
+      </c>
+      <c r="F92" t="s">
+        <v>537</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>539</v>
+      </c>
+      <c r="B93" t="s">
+        <v>540</v>
+      </c>
+      <c r="C93" t="s">
+        <v>164</v>
+      </c>
+      <c r="D93" t="s">
+        <v>165</v>
+      </c>
+      <c r="E93" t="s">
+        <v>541</v>
+      </c>
+      <c r="F93" t="s">
+        <v>542</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>544</v>
+      </c>
+      <c r="B94" t="s">
+        <v>545</v>
+      </c>
+      <c r="C94" t="s">
+        <v>183</v>
+      </c>
+      <c r="D94" t="s">
         <v>546</v>
       </c>
-      <c r="B86" t="s">
+      <c r="E94" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" t="s">
         <v>547</v>
       </c>
-      <c r="C86" t="s">
-        <v>307</v>
-      </c>
-      <c r="D86" t="s">
-        <v>184</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="H94" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="F86" t="s">
-        <v>186</v>
-      </c>
-      <c r="H86" s="2" t="s">
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>549</v>
+      </c>
+      <c r="B95" t="s">
+        <v>550</v>
+      </c>
+      <c r="C95" t="s">
+        <v>551</v>
+      </c>
+      <c r="D95" t="s">
+        <v>165</v>
+      </c>
+      <c r="E95" t="s">
+        <v>270</v>
+      </c>
+      <c r="F95" t="s">
+        <v>552</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>554</v>
+      </c>
+      <c r="B96" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" t="s">
+        <v>230</v>
+      </c>
+      <c r="D96" t="s">
+        <v>165</v>
+      </c>
+      <c r="E96" t="s">
+        <v>213</v>
+      </c>
+      <c r="F96" t="s">
+        <v>555</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>557</v>
+      </c>
+      <c r="B97" t="s">
+        <v>558</v>
+      </c>
+      <c r="C97" t="s">
+        <v>559</v>
+      </c>
+      <c r="D97" t="s">
+        <v>165</v>
+      </c>
+      <c r="E97" t="s">
+        <v>560</v>
+      </c>
+      <c r="F97" t="s">
+        <v>561</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>563</v>
+      </c>
+      <c r="B98" t="s">
+        <v>564</v>
+      </c>
+      <c r="C98" t="s">
+        <v>164</v>
+      </c>
+      <c r="D98" t="s">
+        <v>165</v>
+      </c>
+      <c r="E98" t="s">
+        <v>565</v>
+      </c>
+      <c r="F98" t="s">
+        <v>404</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>567</v>
+      </c>
+      <c r="B99" t="s">
+        <v>264</v>
+      </c>
+      <c r="C99" t="s">
+        <v>183</v>
+      </c>
+      <c r="D99" t="s">
+        <v>165</v>
+      </c>
+      <c r="E99" t="s">
+        <v>568</v>
+      </c>
+      <c r="F99" t="s">
+        <v>266</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>570</v>
+      </c>
+      <c r="B100" t="s">
+        <v>571</v>
+      </c>
+      <c r="C100" t="s">
+        <v>572</v>
+      </c>
+      <c r="D100" t="s">
+        <v>165</v>
+      </c>
+      <c r="E100" t="s">
+        <v>573</v>
+      </c>
+      <c r="F100" t="s">
+        <v>224</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>575</v>
+      </c>
+      <c r="B101" t="s">
+        <v>356</v>
+      </c>
+      <c r="C101" t="s">
+        <v>177</v>
+      </c>
+      <c r="D101" t="s">
+        <v>165</v>
+      </c>
+      <c r="E101" t="s">
+        <v>565</v>
+      </c>
+      <c r="F101" t="s">
+        <v>358</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>577</v>
+      </c>
+      <c r="B102" t="s">
+        <v>578</v>
+      </c>
+      <c r="C102" t="s">
+        <v>164</v>
+      </c>
+      <c r="D102" t="s">
+        <v>194</v>
+      </c>
+      <c r="E102" t="s">
+        <v>44</v>
+      </c>
+      <c r="F102" t="s">
+        <v>487</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>580</v>
+      </c>
+      <c r="B103" t="s">
+        <v>581</v>
+      </c>
+      <c r="C103" t="s">
+        <v>280</v>
+      </c>
+      <c r="D103" t="s">
+        <v>165</v>
+      </c>
+      <c r="E103" t="s">
+        <v>582</v>
+      </c>
+      <c r="F103" t="s">
+        <v>252</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>584</v>
+      </c>
+      <c r="B104" t="s">
+        <v>255</v>
+      </c>
+      <c r="C104" t="s">
+        <v>256</v>
+      </c>
+      <c r="D104" t="s">
+        <v>165</v>
+      </c>
+      <c r="E104" t="s">
+        <v>44</v>
+      </c>
+      <c r="F104" t="s">
+        <v>44</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>586</v>
+      </c>
+      <c r="B105" t="s">
+        <v>587</v>
+      </c>
+      <c r="C105" t="s">
+        <v>177</v>
+      </c>
+      <c r="D105" t="s">
+        <v>165</v>
+      </c>
+      <c r="E105" t="s">
+        <v>588</v>
+      </c>
+      <c r="F105" t="s">
+        <v>589</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>591</v>
+      </c>
+      <c r="B106" t="s">
+        <v>170</v>
+      </c>
+      <c r="C106" t="s">
+        <v>171</v>
+      </c>
+      <c r="D106" t="s">
+        <v>165</v>
+      </c>
+      <c r="E106" t="s">
+        <v>213</v>
+      </c>
+      <c r="F106" t="s">
+        <v>173</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>593</v>
+      </c>
+      <c r="B107" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" t="s">
+        <v>171</v>
+      </c>
+      <c r="D107" t="s">
+        <v>165</v>
+      </c>
+      <c r="E107" t="s">
+        <v>213</v>
+      </c>
+      <c r="F107" t="s">
+        <v>173</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>595</v>
+      </c>
+      <c r="B108" t="s">
+        <v>596</v>
+      </c>
+      <c r="C108" t="s">
+        <v>177</v>
+      </c>
+      <c r="D108" t="s">
+        <v>165</v>
+      </c>
+      <c r="E108" t="s">
+        <v>597</v>
+      </c>
+      <c r="F108" t="s">
+        <v>598</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>600</v>
+      </c>
+      <c r="B109" t="s">
+        <v>601</v>
+      </c>
+      <c r="C109" t="s">
+        <v>602</v>
+      </c>
+      <c r="D109" t="s">
+        <v>165</v>
+      </c>
+      <c r="E109" t="s">
+        <v>603</v>
+      </c>
+      <c r="F109" t="s">
+        <v>604</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>606</v>
+      </c>
+      <c r="B110" t="s">
+        <v>255</v>
+      </c>
+      <c r="C110" t="s">
+        <v>164</v>
+      </c>
+      <c r="D110" t="s">
+        <v>194</v>
+      </c>
+      <c r="E110" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" t="s">
+        <v>44</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>608</v>
+      </c>
+      <c r="B111" t="s">
+        <v>609</v>
+      </c>
+      <c r="C111" t="s">
+        <v>610</v>
+      </c>
+      <c r="D111" t="s">
+        <v>165</v>
+      </c>
+      <c r="E111" t="s">
+        <v>611</v>
+      </c>
+      <c r="F111" t="s">
+        <v>612</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>614</v>
+      </c>
+      <c r="B112" t="s">
+        <v>615</v>
+      </c>
+      <c r="C112" t="s">
+        <v>177</v>
+      </c>
+      <c r="D112" t="s">
+        <v>165</v>
+      </c>
+      <c r="E112" t="s">
+        <v>616</v>
+      </c>
+      <c r="F112" t="s">
+        <v>617</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>619</v>
+      </c>
+      <c r="B113" t="s">
+        <v>620</v>
+      </c>
+      <c r="C113" t="s">
+        <v>621</v>
+      </c>
+      <c r="D113" t="s">
+        <v>194</v>
+      </c>
+      <c r="E113" t="s">
+        <v>622</v>
+      </c>
+      <c r="F113" t="s">
+        <v>623</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>625</v>
+      </c>
+      <c r="B114" t="s">
+        <v>626</v>
+      </c>
+      <c r="C114" t="s">
+        <v>627</v>
+      </c>
+      <c r="D114" t="s">
+        <v>165</v>
+      </c>
+      <c r="E114" t="s">
+        <v>628</v>
+      </c>
+      <c r="F114" t="s">
+        <v>629</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>631</v>
+      </c>
+      <c r="B115" t="s">
+        <v>632</v>
+      </c>
+      <c r="C115" t="s">
+        <v>164</v>
+      </c>
+      <c r="D115" t="s">
+        <v>546</v>
+      </c>
+      <c r="E115" t="s">
+        <v>633</v>
+      </c>
+      <c r="F115" t="s">
+        <v>634</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>636</v>
+      </c>
+      <c r="B116" t="s">
+        <v>637</v>
+      </c>
+      <c r="C116" t="s">
+        <v>177</v>
+      </c>
+      <c r="D116" t="s">
+        <v>165</v>
+      </c>
+      <c r="E116" t="s">
+        <v>638</v>
+      </c>
+      <c r="F116" t="s">
+        <v>639</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>641</v>
+      </c>
+      <c r="B117" t="s">
+        <v>642</v>
+      </c>
+      <c r="C117" t="s">
+        <v>183</v>
+      </c>
+      <c r="D117" t="s">
+        <v>165</v>
+      </c>
+      <c r="E117" t="s">
+        <v>643</v>
+      </c>
+      <c r="F117" t="s">
+        <v>44</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>645</v>
+      </c>
+      <c r="B118" t="s">
+        <v>646</v>
+      </c>
+      <c r="C118" t="s">
+        <v>183</v>
+      </c>
+      <c r="D118" t="s">
+        <v>165</v>
+      </c>
+      <c r="E118" t="s">
+        <v>647</v>
+      </c>
+      <c r="F118" t="s">
+        <v>482</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>649</v>
+      </c>
+      <c r="B119" t="s">
+        <v>650</v>
+      </c>
+      <c r="C119" t="s">
+        <v>164</v>
+      </c>
+      <c r="D119" t="s">
+        <v>194</v>
+      </c>
+      <c r="E119" t="s">
+        <v>651</v>
+      </c>
+      <c r="F119" t="s">
+        <v>652</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>654</v>
+      </c>
+      <c r="B120" t="s">
+        <v>620</v>
+      </c>
+      <c r="C120" t="s">
+        <v>621</v>
+      </c>
+      <c r="D120" t="s">
+        <v>194</v>
+      </c>
+      <c r="E120" t="s">
+        <v>622</v>
+      </c>
+      <c r="F120" t="s">
+        <v>623</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>656</v>
+      </c>
+      <c r="B121" t="s">
+        <v>657</v>
+      </c>
+      <c r="C121" t="s">
+        <v>658</v>
+      </c>
+      <c r="D121" t="s">
+        <v>165</v>
+      </c>
+      <c r="E121" t="s">
+        <v>659</v>
+      </c>
+      <c r="F121" t="s">
+        <v>660</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>662</v>
+      </c>
+      <c r="B122" t="s">
+        <v>663</v>
+      </c>
+      <c r="C122" t="s">
+        <v>164</v>
+      </c>
+      <c r="D122" t="s">
+        <v>546</v>
+      </c>
+      <c r="E122" t="s">
+        <v>664</v>
+      </c>
+      <c r="F122" t="s">
+        <v>665</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>667</v>
+      </c>
+      <c r="B123" t="s">
+        <v>668</v>
+      </c>
+      <c r="C123" t="s">
+        <v>669</v>
+      </c>
+      <c r="D123" t="s">
+        <v>165</v>
+      </c>
+      <c r="E123" t="s">
+        <v>670</v>
+      </c>
+      <c r="F123" t="s">
+        <v>671</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>673</v>
+      </c>
+      <c r="B124" t="s">
+        <v>222</v>
+      </c>
+      <c r="C124" t="s">
+        <v>177</v>
+      </c>
+      <c r="D124" t="s">
+        <v>165</v>
+      </c>
+      <c r="E124" t="s">
+        <v>292</v>
+      </c>
+      <c r="F124" t="s">
+        <v>224</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>675</v>
+      </c>
+      <c r="B125" t="s">
+        <v>676</v>
+      </c>
+      <c r="C125" t="s">
+        <v>177</v>
+      </c>
+      <c r="D125" t="s">
+        <v>165</v>
+      </c>
+      <c r="E125" t="s">
+        <v>677</v>
+      </c>
+      <c r="F125" t="s">
+        <v>44</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>675</v>
+      </c>
+      <c r="B126" t="s">
+        <v>676</v>
+      </c>
+      <c r="C126" t="s">
+        <v>177</v>
+      </c>
+      <c r="D126" t="s">
+        <v>165</v>
+      </c>
+      <c r="E126" t="s">
+        <v>677</v>
+      </c>
+      <c r="F126" t="s">
+        <v>44</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>680</v>
+      </c>
+      <c r="B127" t="s">
+        <v>407</v>
+      </c>
+      <c r="C127" t="s">
+        <v>347</v>
+      </c>
+      <c r="D127" t="s">
+        <v>165</v>
+      </c>
+      <c r="E127" t="s">
+        <v>681</v>
+      </c>
+      <c r="F127" t="s">
+        <v>44</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>683</v>
+      </c>
+      <c r="B128" t="s">
+        <v>684</v>
+      </c>
+      <c r="C128" t="s">
+        <v>685</v>
+      </c>
+      <c r="D128" t="s">
+        <v>165</v>
+      </c>
+      <c r="E128" t="s">
+        <v>686</v>
+      </c>
+      <c r="F128" t="s">
+        <v>687</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>683</v>
+      </c>
+      <c r="B129" t="s">
+        <v>684</v>
+      </c>
+      <c r="C129" t="s">
+        <v>689</v>
+      </c>
+      <c r="D129" t="s">
+        <v>165</v>
+      </c>
+      <c r="E129" t="s">
+        <v>686</v>
+      </c>
+      <c r="F129" t="s">
+        <v>687</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>683</v>
+      </c>
+      <c r="B130" t="s">
+        <v>684</v>
+      </c>
+      <c r="C130" t="s">
+        <v>691</v>
+      </c>
+      <c r="D130" t="s">
+        <v>165</v>
+      </c>
+      <c r="E130" t="s">
+        <v>686</v>
+      </c>
+      <c r="F130" t="s">
+        <v>687</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>693</v>
+      </c>
+      <c r="B131" t="s">
+        <v>694</v>
+      </c>
+      <c r="C131" t="s">
+        <v>164</v>
+      </c>
+      <c r="D131" t="s">
+        <v>546</v>
+      </c>
+      <c r="E131" t="s">
+        <v>695</v>
+      </c>
+      <c r="F131" t="s">
+        <v>696</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>698</v>
+      </c>
+      <c r="B132" t="s">
+        <v>699</v>
+      </c>
+      <c r="C132" t="s">
+        <v>700</v>
+      </c>
+      <c r="D132" t="s">
+        <v>165</v>
+      </c>
+      <c r="E132" t="s">
+        <v>664</v>
+      </c>
+      <c r="F132" t="s">
+        <v>44</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>702</v>
+      </c>
+      <c r="B133" t="s">
+        <v>699</v>
+      </c>
+      <c r="C133" t="s">
+        <v>347</v>
+      </c>
+      <c r="D133" t="s">
+        <v>165</v>
+      </c>
+      <c r="E133" t="s">
+        <v>703</v>
+      </c>
+      <c r="F133" t="s">
+        <v>704</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>706</v>
+      </c>
+      <c r="B134" t="s">
+        <v>707</v>
+      </c>
+      <c r="C134" t="s">
+        <v>164</v>
+      </c>
+      <c r="D134" t="s">
+        <v>165</v>
+      </c>
+      <c r="E134" t="s">
+        <v>708</v>
+      </c>
+      <c r="F134" t="s">
+        <v>709</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>711</v>
+      </c>
+      <c r="B135" t="s">
+        <v>712</v>
+      </c>
+      <c r="C135" t="s">
+        <v>713</v>
+      </c>
+      <c r="D135" t="s">
+        <v>165</v>
+      </c>
+      <c r="E135" t="s">
+        <v>44</v>
+      </c>
+      <c r="F135" t="s">
+        <v>44</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>715</v>
+      </c>
+      <c r="B136" t="s">
+        <v>716</v>
+      </c>
+      <c r="C136" t="s">
+        <v>347</v>
+      </c>
+      <c r="D136" t="s">
+        <v>165</v>
+      </c>
+      <c r="E136" t="s">
+        <v>717</v>
+      </c>
+      <c r="F136" t="s">
+        <v>718</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>720</v>
+      </c>
+      <c r="B137" t="s">
+        <v>511</v>
+      </c>
+      <c r="C137" t="s">
+        <v>721</v>
+      </c>
+      <c r="D137" t="s">
+        <v>165</v>
+      </c>
+      <c r="E137" t="s">
+        <v>722</v>
+      </c>
+      <c r="F137" t="s">
+        <v>514</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>724</v>
+      </c>
+      <c r="B138" t="s">
+        <v>725</v>
+      </c>
+      <c r="C138" t="s">
+        <v>183</v>
+      </c>
+      <c r="D138" t="s">
+        <v>165</v>
+      </c>
+      <c r="E138" t="s">
+        <v>726</v>
+      </c>
+      <c r="F138" t="s">
+        <v>282</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>728</v>
+      </c>
+      <c r="B139" t="s">
+        <v>729</v>
+      </c>
+      <c r="C139" t="s">
+        <v>164</v>
+      </c>
+      <c r="D139" t="s">
+        <v>165</v>
+      </c>
+      <c r="E139" t="s">
+        <v>199</v>
+      </c>
+      <c r="F139" t="s">
+        <v>730</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>728</v>
+      </c>
+      <c r="B140" t="s">
+        <v>732</v>
+      </c>
+      <c r="C140" t="s">
+        <v>733</v>
+      </c>
+      <c r="D140" t="s">
+        <v>165</v>
+      </c>
+      <c r="E140" t="s">
+        <v>734</v>
+      </c>
+      <c r="F140" t="s">
+        <v>735</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>737</v>
+      </c>
+      <c r="B141" t="s">
+        <v>207</v>
+      </c>
+      <c r="C141" t="s">
+        <v>329</v>
+      </c>
+      <c r="D141" t="s">
+        <v>165</v>
+      </c>
+      <c r="E141" t="s">
+        <v>492</v>
+      </c>
+      <c r="F141" t="s">
+        <v>738</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>737</v>
+      </c>
+      <c r="B142" t="s">
+        <v>207</v>
+      </c>
+      <c r="C142" t="s">
+        <v>208</v>
+      </c>
+      <c r="D142" t="s">
+        <v>165</v>
+      </c>
+      <c r="E142" t="s">
+        <v>492</v>
+      </c>
+      <c r="F142" t="s">
+        <v>738</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>737</v>
+      </c>
+      <c r="B143" t="s">
+        <v>207</v>
+      </c>
+      <c r="C143" t="s">
+        <v>177</v>
+      </c>
+      <c r="D143" t="s">
+        <v>165</v>
+      </c>
+      <c r="E143" t="s">
+        <v>492</v>
+      </c>
+      <c r="F143" t="s">
+        <v>738</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>742</v>
+      </c>
+      <c r="B144" t="s">
+        <v>743</v>
+      </c>
+      <c r="C144" t="s">
+        <v>164</v>
+      </c>
+      <c r="D144" t="s">
+        <v>165</v>
+      </c>
+      <c r="E144" t="s">
+        <v>708</v>
+      </c>
+      <c r="F144" t="s">
+        <v>744</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>746</v>
+      </c>
+      <c r="B145" t="s">
+        <v>581</v>
+      </c>
+      <c r="C145" t="s">
+        <v>280</v>
+      </c>
+      <c r="D145" t="s">
+        <v>165</v>
+      </c>
+      <c r="E145" t="s">
+        <v>747</v>
+      </c>
+      <c r="F145" t="s">
+        <v>252</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>749</v>
+      </c>
+      <c r="B146" t="s">
+        <v>534</v>
+      </c>
+      <c r="C146" t="s">
+        <v>535</v>
+      </c>
+      <c r="D146" t="s">
+        <v>165</v>
+      </c>
+      <c r="E146" t="s">
+        <v>750</v>
+      </c>
+      <c r="F146" t="s">
+        <v>537</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>752</v>
+      </c>
+      <c r="B147" t="s">
+        <v>295</v>
+      </c>
+      <c r="C147" t="s">
+        <v>466</v>
+      </c>
+      <c r="D147" t="s">
+        <v>165</v>
+      </c>
+      <c r="E147" t="s">
+        <v>753</v>
+      </c>
+      <c r="F147" t="s">
+        <v>754</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>756</v>
+      </c>
+      <c r="B148" t="s">
+        <v>757</v>
+      </c>
+      <c r="C148" t="s">
+        <v>758</v>
+      </c>
+      <c r="D148" t="s">
+        <v>165</v>
+      </c>
+      <c r="E148" t="s">
+        <v>759</v>
+      </c>
+      <c r="F148" t="s">
+        <v>760</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>762</v>
+      </c>
+      <c r="B149" t="s">
+        <v>511</v>
+      </c>
+      <c r="C149" t="s">
+        <v>721</v>
+      </c>
+      <c r="D149" t="s">
+        <v>165</v>
+      </c>
+      <c r="E149" t="s">
+        <v>763</v>
+      </c>
+      <c r="F149" t="s">
+        <v>514</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>765</v>
+      </c>
+      <c r="B150" t="s">
+        <v>170</v>
+      </c>
+      <c r="C150" t="s">
+        <v>171</v>
+      </c>
+      <c r="D150" t="s">
+        <v>165</v>
+      </c>
+      <c r="E150" t="s">
+        <v>766</v>
+      </c>
+      <c r="F150" t="s">
+        <v>173</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>768</v>
+      </c>
+      <c r="B151" t="s">
+        <v>769</v>
+      </c>
+      <c r="C151" t="s">
+        <v>770</v>
+      </c>
+      <c r="D151" t="s">
+        <v>165</v>
+      </c>
+      <c r="E151" t="s">
+        <v>771</v>
+      </c>
+      <c r="F151" t="s">
+        <v>224</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>773</v>
+      </c>
+      <c r="B152" t="s">
+        <v>774</v>
+      </c>
+      <c r="C152" t="s">
+        <v>775</v>
+      </c>
+      <c r="D152" t="s">
+        <v>165</v>
+      </c>
+      <c r="E152" t="s">
+        <v>261</v>
+      </c>
+      <c r="F152" t="s">
+        <v>487</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>777</v>
+      </c>
+      <c r="B153" t="s">
+        <v>778</v>
+      </c>
+      <c r="C153" t="s">
+        <v>164</v>
+      </c>
+      <c r="D153" t="s">
+        <v>250</v>
+      </c>
+      <c r="E153" t="s">
+        <v>779</v>
+      </c>
+      <c r="F153" t="s">
+        <v>780</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>782</v>
+      </c>
+      <c r="B154" t="s">
+        <v>783</v>
+      </c>
+      <c r="C154" t="s">
+        <v>177</v>
+      </c>
+      <c r="D154" t="s">
+        <v>784</v>
+      </c>
+      <c r="E154" t="s">
+        <v>785</v>
+      </c>
+      <c r="F154" t="s">
+        <v>786</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>788</v>
+      </c>
+      <c r="B155" t="s">
+        <v>789</v>
+      </c>
+      <c r="C155" t="s">
+        <v>790</v>
+      </c>
+      <c r="D155" t="s">
+        <v>165</v>
+      </c>
+      <c r="E155" t="s">
+        <v>791</v>
+      </c>
+      <c r="F155" t="s">
+        <v>792</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>788</v>
+      </c>
+      <c r="B156" t="s">
+        <v>789</v>
+      </c>
+      <c r="C156" t="s">
+        <v>794</v>
+      </c>
+      <c r="D156" t="s">
+        <v>165</v>
+      </c>
+      <c r="E156" t="s">
+        <v>791</v>
+      </c>
+      <c r="F156" t="s">
+        <v>792</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>788</v>
+      </c>
+      <c r="B157" t="s">
+        <v>789</v>
+      </c>
+      <c r="C157" t="s">
+        <v>796</v>
+      </c>
+      <c r="D157" t="s">
+        <v>165</v>
+      </c>
+      <c r="E157" t="s">
+        <v>791</v>
+      </c>
+      <c r="F157" t="s">
+        <v>792</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>788</v>
+      </c>
+      <c r="B158" t="s">
+        <v>789</v>
+      </c>
+      <c r="C158" t="s">
+        <v>798</v>
+      </c>
+      <c r="D158" t="s">
+        <v>165</v>
+      </c>
+      <c r="E158" t="s">
+        <v>791</v>
+      </c>
+      <c r="F158" t="s">
+        <v>792</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>788</v>
+      </c>
+      <c r="B159" t="s">
+        <v>789</v>
+      </c>
+      <c r="C159" t="s">
+        <v>800</v>
+      </c>
+      <c r="D159" t="s">
+        <v>165</v>
+      </c>
+      <c r="E159" t="s">
+        <v>791</v>
+      </c>
+      <c r="F159" t="s">
+        <v>792</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>788</v>
+      </c>
+      <c r="B160" t="s">
+        <v>789</v>
+      </c>
+      <c r="C160" t="s">
+        <v>802</v>
+      </c>
+      <c r="D160" t="s">
+        <v>165</v>
+      </c>
+      <c r="E160" t="s">
+        <v>791</v>
+      </c>
+      <c r="F160" t="s">
+        <v>792</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>788</v>
+      </c>
+      <c r="B161" t="s">
+        <v>789</v>
+      </c>
+      <c r="C161" t="s">
+        <v>804</v>
+      </c>
+      <c r="D161" t="s">
+        <v>165</v>
+      </c>
+      <c r="E161" t="s">
+        <v>791</v>
+      </c>
+      <c r="F161" t="s">
+        <v>792</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>806</v>
+      </c>
+      <c r="B162" t="s">
+        <v>807</v>
+      </c>
+      <c r="C162" t="s">
+        <v>260</v>
+      </c>
+      <c r="D162" t="s">
+        <v>165</v>
+      </c>
+      <c r="E162" t="s">
+        <v>362</v>
+      </c>
+      <c r="F162" t="s">
+        <v>808</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>810</v>
+      </c>
+      <c r="B163" t="s">
+        <v>811</v>
+      </c>
+      <c r="C163" t="s">
+        <v>812</v>
+      </c>
+      <c r="D163" t="s">
+        <v>165</v>
+      </c>
+      <c r="E163" t="s">
+        <v>813</v>
+      </c>
+      <c r="F163" t="s">
+        <v>373</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>815</v>
+      </c>
+      <c r="B164" t="s">
+        <v>816</v>
+      </c>
+      <c r="C164" t="s">
+        <v>183</v>
+      </c>
+      <c r="D164" t="s">
+        <v>165</v>
+      </c>
+      <c r="E164" t="s">
+        <v>817</v>
+      </c>
+      <c r="F164" t="s">
+        <v>44</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>819</v>
+      </c>
+      <c r="B165" t="s">
+        <v>320</v>
+      </c>
+      <c r="C165" t="s">
+        <v>164</v>
+      </c>
+      <c r="D165" t="s">
+        <v>165</v>
+      </c>
+      <c r="E165" t="s">
+        <v>44</v>
+      </c>
+      <c r="F165" t="s">
+        <v>820</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>822</v>
+      </c>
+      <c r="B166" t="s">
+        <v>823</v>
+      </c>
+      <c r="C166" t="s">
+        <v>183</v>
+      </c>
+      <c r="D166" t="s">
+        <v>165</v>
+      </c>
+      <c r="E166" t="s">
+        <v>824</v>
+      </c>
+      <c r="F166" t="s">
+        <v>825</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>827</v>
+      </c>
+      <c r="B167" t="s">
+        <v>828</v>
+      </c>
+      <c r="C167" t="s">
+        <v>217</v>
+      </c>
+      <c r="D167" t="s">
+        <v>165</v>
+      </c>
+      <c r="E167" t="s">
+        <v>829</v>
+      </c>
+      <c r="F167" t="s">
+        <v>830</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>832</v>
+      </c>
+      <c r="B168" t="s">
+        <v>833</v>
+      </c>
+      <c r="C168" t="s">
+        <v>834</v>
+      </c>
+      <c r="D168" t="s">
+        <v>165</v>
+      </c>
+      <c r="E168" t="s">
+        <v>835</v>
+      </c>
+      <c r="F168" t="s">
+        <v>436</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>837</v>
+      </c>
+      <c r="B169" t="s">
+        <v>838</v>
+      </c>
+      <c r="C169" t="s">
+        <v>839</v>
+      </c>
+      <c r="D169" t="s">
+        <v>165</v>
+      </c>
+      <c r="E169" t="s">
+        <v>840</v>
+      </c>
+      <c r="F169" t="s">
+        <v>841</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>843</v>
+      </c>
+      <c r="B170" t="s">
+        <v>375</v>
+      </c>
+      <c r="C170" t="s">
+        <v>844</v>
+      </c>
+      <c r="D170" t="s">
+        <v>165</v>
+      </c>
+      <c r="E170" t="s">
+        <v>845</v>
+      </c>
+      <c r="F170" t="s">
+        <v>846</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>848</v>
+      </c>
+      <c r="B171" t="s">
+        <v>170</v>
+      </c>
+      <c r="C171" t="s">
+        <v>171</v>
+      </c>
+      <c r="D171" t="s">
+        <v>165</v>
+      </c>
+      <c r="E171" t="s">
+        <v>199</v>
+      </c>
+      <c r="F171" t="s">
+        <v>173</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>850</v>
+      </c>
+      <c r="B172" t="s">
+        <v>851</v>
+      </c>
+      <c r="C172" t="s">
+        <v>496</v>
+      </c>
+      <c r="D172" t="s">
+        <v>165</v>
+      </c>
+      <c r="E172" t="s">
+        <v>852</v>
+      </c>
+      <c r="F172" t="s">
+        <v>368</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>854</v>
+      </c>
+      <c r="B173" t="s">
+        <v>855</v>
+      </c>
+      <c r="C173" t="s">
+        <v>856</v>
+      </c>
+      <c r="D173" t="s">
+        <v>165</v>
+      </c>
+      <c r="E173" t="s">
+        <v>44</v>
+      </c>
+      <c r="F173" t="s">
+        <v>44</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>858</v>
+      </c>
+      <c r="B174" t="s">
+        <v>558</v>
+      </c>
+      <c r="C174" t="s">
+        <v>559</v>
+      </c>
+      <c r="D174" t="s">
+        <v>165</v>
+      </c>
+      <c r="E174" t="s">
+        <v>859</v>
+      </c>
+      <c r="F174" t="s">
+        <v>561</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>861</v>
+      </c>
+      <c r="B175" t="s">
+        <v>862</v>
+      </c>
+      <c r="C175" t="s">
+        <v>164</v>
+      </c>
+      <c r="D175" t="s">
+        <v>165</v>
+      </c>
+      <c r="E175" t="s">
+        <v>44</v>
+      </c>
+      <c r="F175" t="s">
+        <v>44</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>864</v>
+      </c>
+      <c r="B176" t="s">
+        <v>865</v>
+      </c>
+      <c r="C176" t="s">
+        <v>177</v>
+      </c>
+      <c r="D176" t="s">
+        <v>165</v>
+      </c>
+      <c r="E176" t="s">
+        <v>866</v>
+      </c>
+      <c r="F176" t="s">
+        <v>867</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>869</v>
+      </c>
+      <c r="B177" t="s">
+        <v>870</v>
+      </c>
+      <c r="C177" t="s">
+        <v>164</v>
+      </c>
+      <c r="D177" t="s">
+        <v>165</v>
+      </c>
+      <c r="E177" t="s">
+        <v>871</v>
+      </c>
+      <c r="F177" t="s">
+        <v>872</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>874</v>
+      </c>
+      <c r="B178" t="s">
+        <v>875</v>
+      </c>
+      <c r="C178" t="s">
+        <v>164</v>
+      </c>
+      <c r="D178" t="s">
+        <v>165</v>
+      </c>
+      <c r="E178" t="s">
+        <v>876</v>
+      </c>
+      <c r="F178" t="s">
+        <v>482</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>878</v>
+      </c>
+      <c r="B179" t="s">
+        <v>879</v>
+      </c>
+      <c r="C179" t="s">
+        <v>880</v>
+      </c>
+      <c r="D179" t="s">
+        <v>165</v>
+      </c>
+      <c r="E179" t="s">
+        <v>881</v>
+      </c>
+      <c r="F179" t="s">
+        <v>882</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>884</v>
+      </c>
+      <c r="B180" t="s">
+        <v>885</v>
+      </c>
+      <c r="C180" t="s">
+        <v>886</v>
+      </c>
+      <c r="D180" t="s">
+        <v>165</v>
+      </c>
+      <c r="E180" t="s">
+        <v>887</v>
+      </c>
+      <c r="F180" t="s">
+        <v>888</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>890</v>
+      </c>
+      <c r="B181" t="s">
+        <v>891</v>
+      </c>
+      <c r="C181" t="s">
+        <v>892</v>
+      </c>
+      <c r="D181" t="s">
+        <v>546</v>
+      </c>
+      <c r="E181" t="s">
+        <v>44</v>
+      </c>
+      <c r="F181" t="s">
+        <v>893</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>895</v>
+      </c>
+      <c r="B182" t="s">
+        <v>896</v>
+      </c>
+      <c r="C182" t="s">
+        <v>188</v>
+      </c>
+      <c r="D182" t="s">
+        <v>250</v>
+      </c>
+      <c r="E182" t="s">
+        <v>897</v>
+      </c>
+      <c r="F182" t="s">
+        <v>252</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>899</v>
+      </c>
+      <c r="B183" t="s">
+        <v>295</v>
+      </c>
+      <c r="C183" t="s">
+        <v>329</v>
+      </c>
+      <c r="D183" t="s">
+        <v>165</v>
+      </c>
+      <c r="E183" t="s">
+        <v>451</v>
+      </c>
+      <c r="F183" t="s">
+        <v>900</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>901</v>
       </c>
     </row>
   </sheetData>
@@ -4877,6 +8164,103 @@
     <hyperlink ref="H84" r:id="rId83"/>
     <hyperlink ref="H85" r:id="rId84"/>
     <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
+    <hyperlink ref="H150" r:id="rId149"/>
+    <hyperlink ref="H151" r:id="rId150"/>
+    <hyperlink ref="H152" r:id="rId151"/>
+    <hyperlink ref="H153" r:id="rId152"/>
+    <hyperlink ref="H154" r:id="rId153"/>
+    <hyperlink ref="H155" r:id="rId154"/>
+    <hyperlink ref="H156" r:id="rId155"/>
+    <hyperlink ref="H157" r:id="rId156"/>
+    <hyperlink ref="H158" r:id="rId157"/>
+    <hyperlink ref="H159" r:id="rId158"/>
+    <hyperlink ref="H160" r:id="rId159"/>
+    <hyperlink ref="H161" r:id="rId160"/>
+    <hyperlink ref="H162" r:id="rId161"/>
+    <hyperlink ref="H163" r:id="rId162"/>
+    <hyperlink ref="H164" r:id="rId163"/>
+    <hyperlink ref="H165" r:id="rId164"/>
+    <hyperlink ref="H166" r:id="rId165"/>
+    <hyperlink ref="H167" r:id="rId166"/>
+    <hyperlink ref="H168" r:id="rId167"/>
+    <hyperlink ref="H169" r:id="rId168"/>
+    <hyperlink ref="H170" r:id="rId169"/>
+    <hyperlink ref="H171" r:id="rId170"/>
+    <hyperlink ref="H172" r:id="rId171"/>
+    <hyperlink ref="H173" r:id="rId172"/>
+    <hyperlink ref="H174" r:id="rId173"/>
+    <hyperlink ref="H175" r:id="rId174"/>
+    <hyperlink ref="H176" r:id="rId175"/>
+    <hyperlink ref="H177" r:id="rId176"/>
+    <hyperlink ref="H178" r:id="rId177"/>
+    <hyperlink ref="H179" r:id="rId178"/>
+    <hyperlink ref="H180" r:id="rId179"/>
+    <hyperlink ref="H181" r:id="rId180"/>
+    <hyperlink ref="H182" r:id="rId181"/>
+    <hyperlink ref="H183" r:id="rId182"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
